--- a/project_final_testcase/Member_5_Final_STQA_Test_Cases.xlsx
+++ b/project_final_testcase/Member_5_Final_STQA_Test_Cases.xlsx
@@ -3,7 +3,13 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="Member 5 Final STQA" sheetId="1" r:id="rId1"/>
+    <sheet name="Overview" sheetId="1" r:id="rId1"/>
+    <sheet name="Test_Cases" sheetId="2" r:id="rId2"/>
+    <sheet name="BVA" sheetId="3" r:id="rId3"/>
+    <sheet name="ECT_DecisionTable" sheetId="4" r:id="rId4"/>
+    <sheet name="Basis_Path" sheetId="5" r:id="rId5"/>
+    <sheet name="Bug_Reports" sheetId="6" r:id="rId6"/>
+    <sheet name="Automation_Coverage" sheetId="7" r:id="rId7"/>
   </sheets>
 </workbook>
 </file>
@@ -397,1515 +403,3048 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O31"/>
+  <dimension ref="A1:D23"/>
   <cols>
-    <col min="1" max="1" width="28.83203125" customWidth="1"/>
-    <col min="2" max="2" width="12.83203125" customWidth="1"/>
-    <col min="3" max="3" width="14.83203125" customWidth="1"/>
-    <col min="4" max="4" width="22.83203125" customWidth="1"/>
-    <col min="5" max="5" width="32.83203125" customWidth="1"/>
-    <col min="6" max="6" width="36.83203125" customWidth="1"/>
-    <col min="7" max="7" width="60.83203125" customWidth="1"/>
-    <col min="8" max="8" width="55.83203125" customWidth="1"/>
-    <col min="9" max="9" width="45.83203125" customWidth="1"/>
-    <col min="10" max="10" width="45.83203125" customWidth="1"/>
-    <col min="11" max="11" width="50.83203125" customWidth="1"/>
-    <col min="12" max="12" width="55.83203125" customWidth="1"/>
-    <col min="13" max="13" width="55.83203125" customWidth="1"/>
-    <col min="14" max="14" width="12.83203125" customWidth="1"/>
-    <col min="15" max="15" width="70.83203125" customWidth="1"/>
+    <col min="1" max="1" width="15.83203125" customWidth="1"/>
+    <col min="2" max="2" width="45.83203125" customWidth="1"/>
+    <col min="3" max="3" width="15.83203125" customWidth="1"/>
+    <col min="4" max="4" width="55.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>Testing Technique</v>
+        <v>Shopfinity — STQA Test Workbook (Member 5)</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>Team and modules</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>Member</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Module</v>
+      </c>
+      <c r="C4" t="str">
+        <v>Test cases</v>
+      </c>
+      <c r="D4" t="str">
+        <v>BVA module</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>Member 5</v>
+      </c>
+      <c r="B5" t="str">
+        <v>Checkout Safety, Payment &amp; Rate Limiting</v>
+      </c>
+      <c r="C5">
+        <v>30</v>
+      </c>
+      <c r="D5" t="str">
+        <v>Checkout — idempotency key length (max 100) &amp; Address/Notes</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>Where each required STQA concept is demonstrated</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>#</v>
+      </c>
+      <c r="B8" t="str">
+        <v>Concept</v>
+      </c>
+      <c r="C8" t="str">
+        <v>Evidence</v>
+      </c>
+      <c r="D8" t="str">
+        <v>Tab / file</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>1</v>
+      </c>
+      <c r="B9" t="str">
+        <v>Boundary Value Analysis (1 module per member)</v>
+      </c>
+      <c r="C9" t="str">
+        <v>5 modules, 32 boundary cases (6-position analysis: min-1, min, min+1, max-1, max, max+1)</v>
+      </c>
+      <c r="D9" t="str">
+        <v>BVA tab; M1_TC_001–005, M2_TC_001–005, M3_TC_001–008, M4_TC_001–008, M5_TC_001–006</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>2</v>
+      </c>
+      <c r="B10" t="str">
+        <v>Equivalence Class Testing / Decision Table</v>
+      </c>
+      <c r="C10" t="str">
+        <v>Equivalence classes across 12 input domains; 4 formal decision tables</v>
+      </c>
+      <c r="D10" t="str">
+        <v>ECT_DecisionTable tab; M1_TC_020–023, M2_TC_018–022, M3_TC_009–014, M4_TC_009–016, M5_TC_019–030</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>3</v>
+      </c>
+      <c r="B11" t="str">
+        <v>Basis Path Testing (5 modules per member)</v>
+      </c>
+      <c r="C11" t="str">
+        <v>25 routine allocations across 5 members (22 unique routines, 5 distinct per member, V(G)=3 to 6)</v>
+      </c>
+      <c r="D11" t="str">
+        <v>Basis_Path tab; M1_TC_006–019, M2_TC_006–017, M3_TC_015–030, M4_TC_017–030, M5_TC_007–018</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>4</v>
+      </c>
+      <c r="B12" t="str">
+        <v>Test Case Design and Execution (30 each)</v>
+      </c>
+      <c r="C12" t="str">
+        <v>30 cases with preconditions, steps, test data, expected/actual result, status, priority</v>
+      </c>
+      <c r="D12" t="str">
+        <v>Test_Cases tab</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>5</v>
+      </c>
+      <c r="B13" t="str">
+        <v>Bug / Defect Reporting (around 30)</v>
+      </c>
+      <c r="C13" t="str">
+        <v>30 verified defects (13 application defects, 11 automation setup issues, 6 rate-limit/infra blockers)</v>
+      </c>
+      <c r="D13" t="str">
+        <v>Bug_Reports tab</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>6</v>
+      </c>
+      <c r="B14" t="str">
+        <v>Unit testing (JUnit / Jest equivalent)</v>
+      </c>
+      <c r="C14" t="str">
+        <v>64 offline unit regression tests (pure logic, schemas, error handler, rate limiter, state machine, service mocks)</v>
+      </c>
+      <c r="D14" t="str">
+        <v>Automation_Coverage tab; tests/phase2a-regression.ts</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>7</v>
+      </c>
+      <c r="B15" t="str">
+        <v>Automation testing (Selenium / Playwright equivalent)</v>
+      </c>
+      <c r="C15" t="str">
+        <v>Playwright E2E and API test suites stored under tests/ root directory</v>
+      </c>
+      <c r="D15" t="str">
+        <v>Automation_Coverage tab; tests/member[1-5]/test_cases/</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>Notes</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>• Exactly 150 test cases total across 5 members (30 per member) derived from actual Shopfinity source code.</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>• Status "Pass" is the result of executed tests (101 verified passes). Cases not executed in the current cycle retain "Not Run" (49 cases) to protect live database integrity.</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>• Automated_By column provides the exact test script path and TC identifier.</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>• Defect_Ref cross-references the Bug_Reports sheet for test cases associated with observed defects.</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>• Basis Path testing evaluates 5 distinct procedural routines per member with cyclomatic complexity V(G) and independent basis paths.</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>• In-memory service mocks (categoryService.update, cartService.mergeCart) are explicitly disclosed as supplementary unit mock evidence.</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:D23"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:N31"/>
+  <cols>
+    <col min="1" max="1" width="12.83203125" customWidth="1"/>
+    <col min="2" max="2" width="12.83203125" customWidth="1"/>
+    <col min="3" max="3" width="28.83203125" customWidth="1"/>
+    <col min="4" max="4" width="16.83203125" customWidth="1"/>
+    <col min="5" max="5" width="45.83203125" customWidth="1"/>
+    <col min="6" max="6" width="35.83203125" customWidth="1"/>
+    <col min="7" max="7" width="55.83203125" customWidth="1"/>
+    <col min="8" max="8" width="35.83203125" customWidth="1"/>
+    <col min="9" max="9" width="55.83203125" customWidth="1"/>
+    <col min="10" max="10" width="55.83203125" customWidth="1"/>
+    <col min="11" max="11" width="10.83203125" customWidth="1"/>
+    <col min="12" max="12" width="10.83203125" customWidth="1"/>
+    <col min="13" max="13" width="45.83203125" customWidth="1"/>
+    <col min="14" max="14" width="12.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>TC_ID</v>
       </c>
       <c r="B1" t="str">
         <v>Member</v>
       </c>
       <c r="C1" t="str">
-        <v>Test ID</v>
+        <v>Module</v>
       </c>
       <c r="D1" t="str">
-        <v>Module</v>
+        <v>Technique</v>
       </c>
       <c r="E1" t="str">
-        <v>Function / Component</v>
+        <v>Title</v>
       </c>
       <c r="F1" t="str">
-        <v>File Path</v>
+        <v>Preconditions</v>
       </c>
       <c r="G1" t="str">
-        <v>Test Case Description</v>
+        <v>Steps</v>
       </c>
       <c r="H1" t="str">
-        <v>Scenario</v>
+        <v>Test_Data</v>
       </c>
       <c r="I1" t="str">
-        <v>Test Data</v>
+        <v>Expected_Result</v>
       </c>
       <c r="J1" t="str">
-        <v>Pre-Condition</v>
+        <v>Actual_Result</v>
       </c>
       <c r="K1" t="str">
-        <v>Steps for Execution</v>
+        <v>Status</v>
       </c>
       <c r="L1" t="str">
-        <v>Expected Result</v>
+        <v>Priority</v>
       </c>
       <c r="M1" t="str">
-        <v>Actual Result</v>
+        <v>Automated_By</v>
       </c>
       <c r="N1" t="str">
-        <v>Status</v>
-      </c>
-      <c r="O1" t="str">
-        <v>Comment</v>
+        <v>Defect_Ref</v>
       </c>
     </row>
     <row r="2" xml:space="preserve">
       <c r="A2" t="str">
-        <v>Boundary Value Analysis (BVA)</v>
+        <v>M5_TC_001</v>
       </c>
       <c r="B2" t="str">
         <v>Member 5</v>
       </c>
       <c r="C2" t="str">
-        <v>M5_TC_001</v>
+        <v>COD Checkout Flow</v>
       </c>
       <c r="D2" t="str">
-        <v>COD Checkout Flow</v>
+        <v>BVA</v>
       </c>
       <c r="E2" t="str">
-        <v>checkoutSchema.shape.shippingAddress (line1)</v>
+        <v>BVA: Shipping address line1 Min-1 (length=0 empty string)</v>
       </c>
       <c r="F2" t="str">
-        <v>lib/validations/order.ts</v>
-      </c>
-      <c r="G2" t="str">
-        <v>BVA: Shipping address line1 Min-1 (length=0 empty string)</v>
-      </c>
-      <c r="H2" t="str">
-        <v>Customer submits checkout with empty address line1</v>
-      </c>
-      <c r="I2" t="str">
-        <v>line1 = ""</v>
-      </c>
-      <c r="J2" t="str">
         <v>Customer at checkout page</v>
       </c>
-      <c r="K2" t="str" xml:space="preserve">
+      <c r="G2" t="str" xml:space="preserve">
         <v xml:space="preserve">1. Submit checkout payload with postalCode: ""
 2. Inspect validation error</v>
       </c>
+      <c r="H2" t="str">
+        <v>line1 = ""</v>
+      </c>
+      <c r="I2" t="str">
+        <v>Validation fails: Address is required (min 1 char)</v>
+      </c>
+      <c r="J2" t="str">
+        <v>Validation error returned on empty line1</v>
+      </c>
+      <c r="K2" t="str">
+        <v>Pass</v>
+      </c>
       <c r="L2" t="str">
-        <v>Validation fails: Address is required (min 1 char)</v>
+        <v>High</v>
       </c>
       <c r="M2" t="str">
-        <v>Validation error returned on empty line1</v>
+        <v>Unit · tests/phase2a-regression.ts · Idempotency &amp; Address Schemas (M5_TC_001)</v>
       </c>
       <c r="N2" t="str">
-        <v>PASS</v>
-      </c>
-      <c r="O2" t="str">
-        <v>Verified via isolated automated test suite (project_final_testcase/member5/test_cases/ &amp; tests/phase2a-regression.ts); not executed against live production database.</v>
+        <v>-</v>
       </c>
     </row>
     <row r="3" xml:space="preserve">
       <c r="A3" t="str">
-        <v>Boundary Value Analysis (BVA)</v>
+        <v>M5_TC_002</v>
       </c>
       <c r="B3" t="str">
         <v>Member 5</v>
       </c>
       <c r="C3" t="str">
-        <v>M5_TC_002</v>
+        <v>COD Checkout Flow</v>
       </c>
       <c r="D3" t="str">
-        <v>COD Checkout Flow</v>
+        <v>BVA</v>
       </c>
       <c r="E3" t="str">
-        <v>checkoutSchema.shape.shippingAddress (line1)</v>
+        <v>BVA: Shipping address line1 Min (length=1)</v>
       </c>
       <c r="F3" t="str">
-        <v>lib/validations/order.ts</v>
-      </c>
-      <c r="G3" t="str">
-        <v>BVA: Shipping address line1 Min (length=1)</v>
-      </c>
-      <c r="H3" t="str">
-        <v>Customer submits checkout with 1-character address line1</v>
-      </c>
-      <c r="I3" t="str">
-        <v>line1 = "A"</v>
-      </c>
-      <c r="J3" t="str">
         <v>Customer at checkout page</v>
       </c>
-      <c r="K3" t="str" xml:space="preserve">
+      <c r="G3" t="str" xml:space="preserve">
         <v xml:space="preserve">1. Submit checkout payload with postalCode: "9"
 2. Verify parse status</v>
       </c>
+      <c r="H3" t="str">
+        <v>line1 = "A"</v>
+      </c>
+      <c r="I3" t="str">
+        <v>Validation succeeds for line1 field</v>
+      </c>
+      <c r="J3" t="str">
+        <v>Accepted 1-character line1 string</v>
+      </c>
+      <c r="K3" t="str">
+        <v>Pass</v>
+      </c>
       <c r="L3" t="str">
-        <v>Validation succeeds for line1 field</v>
+        <v>High</v>
       </c>
       <c r="M3" t="str">
-        <v>Accepted 1-character line1 string</v>
+        <v>Unit · tests/phase2a-regression.ts · Idempotency &amp; Address Schemas (M5_TC_002)</v>
       </c>
       <c r="N3" t="str">
-        <v>PASS</v>
-      </c>
-      <c r="O3" t="str">
-        <v>Verified via isolated automated test suite (project_final_testcase/member5/test_cases/ &amp; tests/phase2a-regression.ts); not executed against live production database.</v>
+        <v>-</v>
       </c>
     </row>
     <row r="4" xml:space="preserve">
       <c r="A4" t="str">
-        <v>Boundary Value Analysis (BVA)</v>
+        <v>M5_TC_003</v>
       </c>
       <c r="B4" t="str">
         <v>Member 5</v>
       </c>
       <c r="C4" t="str">
-        <v>M5_TC_003</v>
+        <v>COD Checkout Flow</v>
       </c>
       <c r="D4" t="str">
-        <v>COD Checkout Flow</v>
+        <v>BVA</v>
       </c>
       <c r="E4" t="str">
-        <v>checkoutSchema.notes</v>
+        <v>BVA: Checkout notes length Max (length=500)</v>
       </c>
       <c r="F4" t="str">
-        <v>lib/validations/order.ts</v>
-      </c>
-      <c r="G4" t="str">
-        <v>BVA: Checkout notes length Max (length=500)</v>
-      </c>
-      <c r="H4" t="str">
-        <v>Customer submits checkout notes at maximum allowed ceiling</v>
-      </c>
-      <c r="I4" t="str">
-        <v>notes = "N" repeated 500 times</v>
-      </c>
-      <c r="J4" t="str">
         <v>Customer at checkout page</v>
       </c>
-      <c r="K4" t="str" xml:space="preserve">
+      <c r="G4" t="str" xml:space="preserve">
         <v xml:space="preserve">1. Submit checkout payload with phone: ""
 2. Inspect validation error</v>
       </c>
+      <c r="H4" t="str">
+        <v>notes = "N" repeated 500 times</v>
+      </c>
+      <c r="I4" t="str">
+        <v>Validation succeeds; notes accepted within 500-char limit</v>
+      </c>
+      <c r="J4" t="str">
+        <v>Accepted 500-character notes string</v>
+      </c>
+      <c r="K4" t="str">
+        <v>Pass</v>
+      </c>
       <c r="L4" t="str">
-        <v>Validation succeeds; notes accepted within 500-char limit</v>
+        <v>High</v>
       </c>
       <c r="M4" t="str">
-        <v>Accepted 500-character notes string</v>
+        <v>Unit · tests/phase2a-regression.ts · Idempotency &amp; Address Schemas (M5_TC_003)</v>
       </c>
       <c r="N4" t="str">
-        <v>PASS</v>
-      </c>
-      <c r="O4" t="str">
-        <v>Verified via isolated automated test suite (project_final_testcase/member5/test_cases/ &amp; tests/phase2a-regression.ts); not executed against live production database.</v>
+        <v>-</v>
       </c>
     </row>
     <row r="5" xml:space="preserve">
       <c r="A5" t="str">
-        <v>Boundary Value Analysis (BVA)</v>
+        <v>M5_TC_004</v>
       </c>
       <c r="B5" t="str">
         <v>Member 5</v>
       </c>
       <c r="C5" t="str">
-        <v>M5_TC_004</v>
+        <v>COD Checkout Flow</v>
       </c>
       <c r="D5" t="str">
-        <v>COD Checkout Flow</v>
+        <v>BVA</v>
       </c>
       <c r="E5" t="str">
-        <v>checkoutSchema.notes</v>
+        <v>BVA: Checkout notes length Max+1 (length=501)</v>
       </c>
       <c r="F5" t="str">
-        <v>lib/validations/order.ts</v>
-      </c>
-      <c r="G5" t="str">
-        <v>BVA: Checkout notes length Max+1 (length=501)</v>
-      </c>
-      <c r="H5" t="str">
-        <v>Customer submits checkout notes exceeding 500 characters</v>
-      </c>
-      <c r="I5" t="str">
-        <v>notes = "N" repeated 501 times</v>
-      </c>
-      <c r="J5" t="str">
         <v>Customer at checkout page</v>
       </c>
-      <c r="K5" t="str" xml:space="preserve">
+      <c r="G5" t="str" xml:space="preserve">
         <v xml:space="preserve">1. Submit checkout payload with phone: "+1-555-0199"
 2. Verify parse status</v>
       </c>
+      <c r="H5" t="str">
+        <v>notes = "N" repeated 501 times</v>
+      </c>
+      <c r="I5" t="str">
+        <v>Validation fails: notes must be at most 500 characters</v>
+      </c>
+      <c r="J5" t="str">
+        <v>Validation error returned rejecting notes &gt;500 chars</v>
+      </c>
+      <c r="K5" t="str">
+        <v>Pass</v>
+      </c>
       <c r="L5" t="str">
-        <v>Validation fails: notes must be at most 500 characters</v>
+        <v>High</v>
       </c>
       <c r="M5" t="str">
-        <v>Validation error returned rejecting notes &gt;500 chars</v>
+        <v>Unit · tests/phase2a-regression.ts · Idempotency &amp; Address Schemas (M5_TC_004)</v>
       </c>
       <c r="N5" t="str">
-        <v>PASS</v>
-      </c>
-      <c r="O5" t="str">
-        <v>Verified via isolated automated test suite (project_final_testcase/member5/test_cases/ &amp; tests/phase2a-regression.ts); not executed against live production database.</v>
+        <v>-</v>
       </c>
     </row>
     <row r="6" xml:space="preserve">
       <c r="A6" t="str">
-        <v>Boundary Value Analysis (BVA)</v>
+        <v>M5_TC_005</v>
       </c>
       <c r="B6" t="str">
         <v>Member 5</v>
       </c>
       <c r="C6" t="str">
-        <v>M5_TC_005</v>
+        <v>Checkout Idempotency</v>
       </c>
       <c r="D6" t="str">
-        <v>Checkout Idempotency</v>
+        <v>BVA</v>
       </c>
       <c r="E6" t="str">
-        <v>checkoutSchema.idempotencyKey</v>
+        <v>BVA: idempotencyKey length Max (length=100)</v>
       </c>
       <c r="F6" t="str">
-        <v>lib/validations/order.ts</v>
-      </c>
-      <c r="G6" t="str">
-        <v>BVA: idempotencyKey length Max (length=100)</v>
-      </c>
-      <c r="H6" t="str">
-        <v>Client generates idempotency key with maximum allowed length</v>
-      </c>
-      <c r="I6" t="str">
-        <v>idempotencyKey = "K" repeated 100 times</v>
-      </c>
-      <c r="J6" t="str">
         <v>Client submitting checkout</v>
       </c>
-      <c r="K6" t="str" xml:space="preserve">
+      <c r="G6" t="str" xml:space="preserve">
         <v xml:space="preserve">1. Parse checkoutSchema with 100-character idempotencyKey
 2. Verify parse status</v>
       </c>
+      <c r="H6" t="str">
+        <v>idempotencyKey = "K" repeated 100 times</v>
+      </c>
+      <c r="I6" t="str">
+        <v>Validation succeeds; key accepted within 100-char limit</v>
+      </c>
+      <c r="J6" t="str">
+        <v>Accepted 100-character idempotency key</v>
+      </c>
+      <c r="K6" t="str">
+        <v>Pass</v>
+      </c>
       <c r="L6" t="str">
-        <v>Validation succeeds; key accepted within 100-char limit</v>
+        <v>High</v>
       </c>
       <c r="M6" t="str">
-        <v>Accepted 100-character idempotency key</v>
+        <v>Unit · tests/phase2a-regression.ts · Idempotency &amp; Address Schemas (M5_TC_005)</v>
       </c>
       <c r="N6" t="str">
-        <v>PASS</v>
-      </c>
-      <c r="O6" t="str">
-        <v>Verified via isolated automated test suite (project_final_testcase/member5/test_cases/ &amp; tests/phase2a-regression.ts); not executed against live production database.</v>
+        <v>-</v>
       </c>
     </row>
     <row r="7" xml:space="preserve">
       <c r="A7" t="str">
-        <v>Boundary Value Analysis (BVA)</v>
+        <v>M5_TC_006</v>
       </c>
       <c r="B7" t="str">
         <v>Member 5</v>
       </c>
       <c r="C7" t="str">
-        <v>M5_TC_006</v>
+        <v>Checkout Idempotency</v>
       </c>
       <c r="D7" t="str">
-        <v>Checkout Idempotency</v>
+        <v>BVA</v>
       </c>
       <c r="E7" t="str">
-        <v>checkoutSchema.idempotencyKey</v>
+        <v>BVA: idempotencyKey length Max+1 (length=101)</v>
       </c>
       <c r="F7" t="str">
-        <v>lib/validations/order.ts</v>
-      </c>
-      <c r="G7" t="str">
-        <v>BVA: idempotencyKey length Max+1 (length=101)</v>
-      </c>
-      <c r="H7" t="str">
-        <v>Client submits idempotency key exceeding 100 characters</v>
-      </c>
-      <c r="I7" t="str">
-        <v>idempotencyKey = "K" repeated 101 times</v>
-      </c>
-      <c r="J7" t="str">
         <v>Client submitting checkout</v>
       </c>
-      <c r="K7" t="str" xml:space="preserve">
+      <c r="G7" t="str" xml:space="preserve">
         <v xml:space="preserve">1. Parse checkoutSchema with 101-character idempotencyKey
 2. Inspect validation error</v>
       </c>
+      <c r="H7" t="str">
+        <v>idempotencyKey = "K" repeated 101 times</v>
+      </c>
+      <c r="I7" t="str">
+        <v>Validation fails: idempotencyKey must be at most 100 characters</v>
+      </c>
+      <c r="J7" t="str">
+        <v>Validation rejected key exceeding 100 characters</v>
+      </c>
+      <c r="K7" t="str">
+        <v>Pass</v>
+      </c>
       <c r="L7" t="str">
-        <v>Validation fails: idempotencyKey must be at most 100 characters</v>
+        <v>High</v>
       </c>
       <c r="M7" t="str">
-        <v>Validation rejected key exceeding 100 characters</v>
+        <v>Unit · tests/phase2a-regression.ts · Idempotency &amp; Address Schemas (M5_TC_006)</v>
       </c>
       <c r="N7" t="str">
-        <v>PASS</v>
-      </c>
-      <c r="O7" t="str">
-        <v>Verified via isolated automated test suite (project_final_testcase/member5/test_cases/ &amp; tests/phase2a-regression.ts); not executed against live production database.</v>
+        <v>-</v>
       </c>
     </row>
     <row r="8" xml:space="preserve">
       <c r="A8" t="str">
-        <v>Basis Path Testing (BP)</v>
+        <v>M5_TC_007</v>
       </c>
       <c r="B8" t="str">
         <v>Member 5</v>
       </c>
       <c r="C8" t="str">
-        <v>M5_TC_007</v>
+        <v>Checkout Idempotency</v>
       </c>
       <c r="D8" t="str">
-        <v>Checkout Idempotency</v>
+        <v>Basis Path</v>
       </c>
       <c r="E8" t="str">
-        <v>orderService.checkout</v>
+        <v>BP: Idempotency Path 1 - Client key exists for same user returns cached order</v>
       </c>
       <c r="F8" t="str">
-        <v>lib/services/order-service.ts</v>
-      </c>
-      <c r="G8" t="str">
-        <v>BP: Idempotency Path 1 - Client key exists for same user returns cached order</v>
-      </c>
-      <c r="H8" t="str">
-        <v>Customer network timeout causes retry of identical checkout request</v>
-      </c>
-      <c r="I8" t="str">
-        <v>idempotencyKey = "unique-key-001", userId = "user-1"</v>
-      </c>
-      <c r="J8" t="str">
         <v>Order previously created with "unique-key-001" by "user-1"</v>
       </c>
-      <c r="K8" t="str" xml:space="preserve">
+      <c r="G8" t="str" xml:space="preserve">
         <v xml:space="preserve">1. Execute orderService.checkout("user-1", { idempotencyKey: "unique-key-001" })
 2. Compare returned order</v>
       </c>
+      <c r="H8" t="str">
+        <v>idempotencyKey = "unique-key-001", userId = "user-1"</v>
+      </c>
+      <c r="I8" t="str">
+        <v>Returns existing order without performing database transaction or re-decrementing stock</v>
+      </c>
+      <c r="J8" t="str">
+        <v>Cached order returned, duplicate write prevented</v>
+      </c>
+      <c r="K8" t="str">
+        <v>Pass</v>
+      </c>
       <c r="L8" t="str">
-        <v>Returns existing order without performing database transaction or re-decrementing stock</v>
+        <v>High</v>
       </c>
       <c r="M8" t="str">
-        <v>Cached order returned, duplicate write prevented</v>
+        <v>Unit · tests/phase2a-regression.ts · COD Checkout &amp; Idempotency (M5_TC_007)</v>
       </c>
       <c r="N8" t="str">
-        <v>PASS</v>
-      </c>
-      <c r="O8" t="str">
-        <v>Verified via isolated automated test suite (project_final_testcase/member5/test_cases/ &amp; tests/phase2a-regression.ts); not executed against live production database.</v>
+        <v>-</v>
       </c>
     </row>
     <row r="9" xml:space="preserve">
       <c r="A9" t="str">
-        <v>Basis Path Testing (BP)</v>
+        <v>M5_TC_008</v>
       </c>
       <c r="B9" t="str">
         <v>Member 5</v>
       </c>
       <c r="C9" t="str">
-        <v>M5_TC_008</v>
+        <v>Checkout Idempotency</v>
       </c>
       <c r="D9" t="str">
-        <v>Checkout Idempotency</v>
+        <v>Basis Path</v>
       </c>
       <c r="E9" t="str">
-        <v>orderService.checkout</v>
+        <v>BP: Idempotency Path 2 - Cross-user key collision throws ConflictError</v>
       </c>
       <c r="F9" t="str">
-        <v>lib/services/order-service.ts</v>
-      </c>
-      <c r="G9" t="str">
-        <v>BP: Idempotency Path 2 - Cross-user key collision throws ConflictError</v>
-      </c>
-      <c r="H9" t="str">
-        <v>Malicious client or collision presents idempotency key belonging to another user</v>
-      </c>
-      <c r="I9" t="str">
-        <v>idempotencyKey = "key-owned-by-user-1", userId = "user-2"</v>
-      </c>
-      <c r="J9" t="str">
         <v>Key "key-owned-by-user-1" was used by user-1</v>
       </c>
-      <c r="K9" t="str" xml:space="preserve">
+      <c r="G9" t="str" xml:space="preserve">
         <v xml:space="preserve">1. Execute orderService.checkout("user-2", { idempotencyKey: "key-owned-by-user-1" })
 2. Catch exception</v>
       </c>
+      <c r="H9" t="str">
+        <v>idempotencyKey = "key-owned-by-user-1", userId = "user-2"</v>
+      </c>
+      <c r="I9" t="str">
+        <v>Throws ConflictError("Idempotency key has already been used for a different request")</v>
+      </c>
+      <c r="J9" t="str">
+        <v>ConflictError thrown, cross-tenant key hijack blocked</v>
+      </c>
+      <c r="K9" t="str">
+        <v>Pass</v>
+      </c>
       <c r="L9" t="str">
-        <v>Throws ConflictError("Idempotency key has already been used for a different request")</v>
+        <v>High</v>
       </c>
       <c r="M9" t="str">
-        <v>ConflictError thrown, cross-tenant key hijack blocked</v>
+        <v>Unit · tests/phase2a-regression.ts · COD Checkout &amp; Idempotency (M5_TC_008)</v>
       </c>
       <c r="N9" t="str">
-        <v>PASS</v>
-      </c>
-      <c r="O9" t="str">
-        <v>Verified via isolated automated test suite (project_final_testcase/member5/test_cases/ &amp; tests/phase2a-regression.ts); not executed against live production database.</v>
+        <v>-</v>
       </c>
     </row>
     <row r="10" xml:space="preserve">
       <c r="A10" t="str">
-        <v>Basis Path Testing (BP)</v>
+        <v>M5_TC_009</v>
       </c>
       <c r="B10" t="str">
         <v>Member 5</v>
       </c>
       <c r="C10" t="str">
-        <v>M5_TC_009</v>
+        <v>COD Checkout Flow</v>
       </c>
       <c r="D10" t="str">
-        <v>COD Checkout Flow</v>
+        <v>Basis Path</v>
       </c>
       <c r="E10" t="str">
-        <v>orderService.checkout</v>
+        <v>BP: Checkout Path 1 - Cart is empty or missing throws NotFoundError</v>
       </c>
       <c r="F10" t="str">
-        <v>lib/services/order-service.ts</v>
-      </c>
-      <c r="G10" t="str">
-        <v>BP: Checkout Path 1 - Cart is empty or missing throws NotFoundError</v>
-      </c>
-      <c r="H10" t="str">
-        <v>Customer submits checkout with no items in cart</v>
-      </c>
-      <c r="I10" t="str">
-        <v>Cart has items = []</v>
-      </c>
-      <c r="J10" t="str">
         <v>User cart is empty</v>
       </c>
-      <c r="K10" t="str" xml:space="preserve">
+      <c r="G10" t="str" xml:space="preserve">
         <v xml:space="preserve">1. Execute orderService.checkout(userId, {})
 2. Catch exception</v>
       </c>
+      <c r="H10" t="str">
+        <v>Cart has items = []</v>
+      </c>
+      <c r="I10" t="str">
+        <v>Throws NotFoundError("Cart", "empty")</v>
+      </c>
+      <c r="J10" t="str">
+        <v>NotFoundError thrown as expected</v>
+      </c>
+      <c r="K10" t="str">
+        <v>Pass</v>
+      </c>
       <c r="L10" t="str">
-        <v>Throws NotFoundError("Cart", "empty")</v>
+        <v>High</v>
       </c>
       <c r="M10" t="str">
-        <v>NotFoundError thrown as expected</v>
+        <v>Unit · tests/phase2a-regression.ts · COD Checkout &amp; Idempotency (M5_TC_009)</v>
       </c>
       <c r="N10" t="str">
-        <v>PASS</v>
-      </c>
-      <c r="O10" t="str">
-        <v>Verified via isolated automated test suite (project_final_testcase/member5/test_cases/ &amp; tests/phase2a-regression.ts); not executed against live production database.</v>
+        <v>-</v>
       </c>
     </row>
     <row r="11" xml:space="preserve">
       <c r="A11" t="str">
-        <v>Basis Path Testing (BP)</v>
+        <v>M5_TC_010</v>
       </c>
       <c r="B11" t="str">
         <v>Member 5</v>
       </c>
       <c r="C11" t="str">
-        <v>M5_TC_010</v>
+        <v>COD Checkout Flow</v>
       </c>
       <c r="D11" t="str">
-        <v>COD Checkout Flow</v>
+        <v>Basis Path</v>
       </c>
       <c r="E11" t="str">
-        <v>orderService.checkout</v>
+        <v>BP: Checkout Path 2 - Cart contains soft-deleted product throws NotFoundError</v>
       </c>
       <c r="F11" t="str">
-        <v>lib/services/order-service.ts</v>
-      </c>
-      <c r="G11" t="str">
-        <v>BP: Checkout Path 2 - Cart contains soft-deleted product throws NotFoundError</v>
-      </c>
-      <c r="H11" t="str">
-        <v>Admin soft-deletes a product while it sits in customer cart before checkout</v>
-      </c>
-      <c r="I11" t="str">
-        <v>item.product has isDeleted=true</v>
-      </c>
-      <c r="J11" t="str">
         <v>Product was deleted in database</v>
       </c>
-      <c r="K11" t="str" xml:space="preserve">
+      <c r="G11" t="str" xml:space="preserve">
         <v xml:space="preserve">1. Execute orderService.checkout(userId, {})
 2. Catch exception</v>
       </c>
+      <c r="H11" t="str">
+        <v>item.product has isDeleted=true</v>
+      </c>
+      <c r="I11" t="str">
+        <v>Throws NotFoundError for unavailable product; halts with zero partial writes</v>
+      </c>
+      <c r="J11" t="str">
+        <v>NotFoundError thrown, zero partial writes</v>
+      </c>
+      <c r="K11" t="str">
+        <v>Pass</v>
+      </c>
       <c r="L11" t="str">
-        <v>Throws NotFoundError for unavailable product; halts with zero partial writes</v>
+        <v>High</v>
       </c>
       <c r="M11" t="str">
-        <v>NotFoundError thrown, zero partial writes</v>
+        <v>Unit · tests/phase2a-regression.ts · COD Checkout &amp; Idempotency (M5_TC_010)</v>
       </c>
       <c r="N11" t="str">
-        <v>PASS</v>
-      </c>
-      <c r="O11" t="str">
-        <v>Verified via isolated automated test suite (project_final_testcase/member5/test_cases/ &amp; tests/phase2a-regression.ts); not executed against live production database.</v>
+        <v>-</v>
       </c>
     </row>
     <row r="12" xml:space="preserve">
       <c r="A12" t="str">
-        <v>Basis Path Testing (BP)</v>
+        <v>M5_TC_011</v>
       </c>
       <c r="B12" t="str">
         <v>Member 5</v>
       </c>
       <c r="C12" t="str">
-        <v>M5_TC_011</v>
+        <v>COD Checkout Flow</v>
       </c>
       <c r="D12" t="str">
-        <v>COD Checkout Flow</v>
+        <v>Basis Path</v>
       </c>
       <c r="E12" t="str">
-        <v>orderService.checkout</v>
+        <v>BP: Checkout Path 3 - Product stock insufficient throws ConflictError</v>
       </c>
       <c r="F12" t="str">
-        <v>lib/services/order-service.ts</v>
-      </c>
-      <c r="G12" t="str">
-        <v>BP: Checkout Path 3 - Product stock insufficient throws ConflictError</v>
-      </c>
-      <c r="H12" t="str">
-        <v>Cart quantity exceeds current warehouse stock at checkout execution</v>
-      </c>
-      <c r="I12" t="str">
-        <v>stockQuantity = 2, requested quantity = 3</v>
-      </c>
-      <c r="J12" t="str">
         <v>Product stock is 2</v>
       </c>
-      <c r="K12" t="str" xml:space="preserve">
+      <c r="G12" t="str" xml:space="preserve">
         <v xml:space="preserve">1. Execute orderService.checkout(userId, {})
 2. Catch exception</v>
       </c>
+      <c r="H12" t="str">
+        <v>stockQuantity = 2, requested quantity = 3</v>
+      </c>
+      <c r="I12" t="str">
+        <v>Throws ConflictError("Insufficient stock for "...""); transaction rolls back</v>
+      </c>
+      <c r="J12" t="str">
+        <v>ConflictError thrown, stock boundaries guarded</v>
+      </c>
+      <c r="K12" t="str">
+        <v>Pass</v>
+      </c>
       <c r="L12" t="str">
-        <v>Throws ConflictError("Insufficient stock for "...""); transaction rolls back</v>
+        <v>High</v>
       </c>
       <c r="M12" t="str">
-        <v>ConflictError thrown, stock boundaries guarded</v>
+        <v>Unit · tests/phase2a-regression.ts · COD Checkout &amp; Idempotency (M5_TC_011)</v>
       </c>
       <c r="N12" t="str">
-        <v>PASS</v>
-      </c>
-      <c r="O12" t="str">
-        <v>Verified via isolated automated test suite (project_final_testcase/member5/test_cases/ &amp; tests/phase2a-regression.ts); not executed against live production database.</v>
+        <v>-</v>
       </c>
     </row>
     <row r="13" xml:space="preserve">
       <c r="A13" t="str">
-        <v>Basis Path Testing (BP)</v>
+        <v>M5_TC_012</v>
       </c>
       <c r="B13" t="str">
         <v>Member 5</v>
       </c>
       <c r="C13" t="str">
-        <v>M5_TC_012</v>
+        <v>Error Handling Infrastructure</v>
       </c>
       <c r="D13" t="str">
-        <v>COD Checkout Flow</v>
+        <v>Basis Path</v>
       </c>
       <c r="E13" t="str">
-        <v>orderService.checkout</v>
+        <v>BP: handleApiError Path 4 - JSON payload SyntaxError mapped to 400 Bad Request</v>
       </c>
       <c r="F13" t="str">
-        <v>lib/services/order-service.ts</v>
-      </c>
-      <c r="G13" t="str">
-        <v>BP: Checkout Path 4 - Valid checkout with shipping address creates order and decrements stock</v>
+        <v>API route wrapped with handleApiError middleware</v>
+      </c>
+      <c r="G13" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Dispatch HTTP request with malformed JSON body to API route.
+2. Request parser throws SyntaxError.
+3. handleApiError catches error and evaluates instanceof SyntaxError &amp;&amp; 'body' in error.
+4. Return formatted NextResponse.</v>
       </c>
       <c r="H13" t="str">
-        <v>Customer submits COD checkout with delivery address and available items</v>
+        <v>Request payload with malformed JSON syntax: '{"invalid": }'</v>
       </c>
       <c r="I13" t="str">
-        <v>Valid shipping address, 2 items in stock</v>
+        <v>Returns HTTP 400 Bad Request with JSON code "BAD_REQUEST" and message "Invalid JSON payload in request body"</v>
       </c>
       <c r="J13" t="str">
-        <v>Items in stock; valid delivery address</v>
-      </c>
-      <c r="K13" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Execute orderService.checkout(userId, inputWithAddress)
-2. Inspect database transaction result</v>
+        <v>Verified passing in automated regression suite (tests/phase2a-regression.ts:218-223): Malformed JSON SyntaxError correctly caught and mapped to HTTP 400 Bad Request with code BAD_REQUEST.</v>
+      </c>
+      <c r="K13" t="str">
+        <v>Pass</v>
       </c>
       <c r="L13" t="str">
-        <v>Creates Address, Order (Pending), OrderItems, decrements product stockQuantity, clears CartItem records</v>
+        <v>Medium</v>
       </c>
       <c r="M13" t="str">
-        <v>Not Run</v>
+        <v>Unit · tests/phase2a-regression.ts · handleApiError &amp; apiHandler (M5_TC_012)</v>
       </c>
       <c r="N13" t="str">
-        <v>Not Run</v>
-      </c>
-      <c r="O13" t="str">
-        <v>Unexecuted against live Vercel environment to adhere to project safety constraints (prohibiting production DB mutations / synthetic orders). Retained as validated specification.</v>
+        <v>-</v>
       </c>
     </row>
     <row r="14" xml:space="preserve">
       <c r="A14" t="str">
-        <v>Basis Path Testing (BP)</v>
+        <v>M5_TC_013</v>
       </c>
       <c r="B14" t="str">
         <v>Member 5</v>
       </c>
       <c r="C14" t="str">
-        <v>M5_TC_013</v>
+        <v>Security &amp; Rate Limiting</v>
       </c>
       <c r="D14" t="str">
-        <v>COD Checkout Flow</v>
+        <v>Basis Path</v>
       </c>
       <c r="E14" t="str">
-        <v>orderService.checkout</v>
+        <v>BP: rateLimit Path 3 - Sliding window quota exceeded rejects request with 429</v>
       </c>
       <c r="F14" t="str">
-        <v>lib/services/order-service.ts</v>
-      </c>
-      <c r="G14" t="str">
-        <v>BP: Checkout Path 5 - Valid checkout without shipping address creates order with null addressId</v>
+        <v>Rate limiter initialized with clean in-memory map</v>
+      </c>
+      <c r="G14" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Initialize rateLimit with limit=5.
+2. Dispatch 5 requests for identifier (all succeed with remaining &gt;= 0).
+3. Dispatch 6th request exceeding limit quota.
+4. Verify rateLimit response.</v>
       </c>
       <c r="H14" t="str">
-        <v>Customer submits checkout with digital or omitted shipping address</v>
+        <v>identifier: "test-ip-client", limit: 5, windowMs: 60000, 6 requests dispatched</v>
       </c>
       <c r="I14" t="str">
-        <v>shippingAddress = undefined</v>
+        <v>Rate limiter returns { allowed: false, remaining: 0, resetIn: &gt; 0 }; API route returns HTTP 429 Too Many Requests</v>
       </c>
       <c r="J14" t="str">
-        <v>Items in stock</v>
-      </c>
-      <c r="K14" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Execute orderService.checkout(userId, inputWithoutAddress)
-2. Inspect created order</v>
+        <v>Verified passing in automated regression suite (tests/phase2a-regression.ts:1002-1016): rate limiter allows quota within window and returns allowed: false when limit exceeded.</v>
+      </c>
+      <c r="K14" t="str">
+        <v>Pass</v>
       </c>
       <c r="L14" t="str">
-        <v>Order created with shippingAddressId=undefined; status=Pending; stock decremented</v>
+        <v>Medium</v>
       </c>
       <c r="M14" t="str">
-        <v>Not Run</v>
+        <v>Unit · tests/phase2a-regression.ts · rateLimit &amp; rateLimitResponse (M5_TC_013)</v>
       </c>
       <c r="N14" t="str">
-        <v>Not Run</v>
-      </c>
-      <c r="O14" t="str">
-        <v>Unexecuted against live Vercel environment to adhere to project safety constraints (prohibiting production DB mutations / synthetic orders). Retained as validated specification.</v>
+        <v>-</v>
       </c>
     </row>
     <row r="15" xml:space="preserve">
       <c r="A15" t="str">
-        <v>Basis Path Testing (BP)</v>
+        <v>M5_TC_014</v>
       </c>
       <c r="B15" t="str">
         <v>Member 5</v>
       </c>
       <c r="C15" t="str">
-        <v>M5_TC_014</v>
+        <v>Order Status &amp; Cancellation</v>
       </c>
       <c r="D15" t="str">
-        <v>Order Status &amp; Cancellation</v>
+        <v>Basis Path</v>
       </c>
       <c r="E15" t="str">
-        <v>orderService.updateStatus</v>
+        <v>BP: updateStatus Path 1 - Order not found throws NotFoundError</v>
       </c>
       <c r="F15" t="str">
-        <v>lib/services/order-service.ts</v>
-      </c>
-      <c r="G15" t="str">
-        <v>BP: updateStatus Path 1 - Order not found throws NotFoundError</v>
-      </c>
-      <c r="H15" t="str">
-        <v>Updating status for non-existent order ID</v>
-      </c>
-      <c r="I15" t="str">
-        <v>orderId = "invalid-order-uuid"</v>
-      </c>
-      <c r="J15" t="str">
         <v>Order does not exist in DB</v>
       </c>
-      <c r="K15" t="str" xml:space="preserve">
+      <c r="G15" t="str" xml:space="preserve">
         <v xml:space="preserve">1. Call orderService.updateStatus("invalid-order-uuid", "Shipped")
 2. Catch exception</v>
       </c>
+      <c r="H15" t="str">
+        <v>orderId = "invalid-order-uuid"</v>
+      </c>
+      <c r="I15" t="str">
+        <v>Throws NotFoundError("Order", "invalid-order-uuid")</v>
+      </c>
+      <c r="J15" t="str">
+        <v>Not Run</v>
+      </c>
+      <c r="K15" t="str">
+        <v>Not Run</v>
+      </c>
       <c r="L15" t="str">
-        <v>Throws NotFoundError("Order", "invalid-order-uuid")</v>
+        <v>Medium</v>
       </c>
       <c r="M15" t="str">
-        <v>Not Run</v>
+        <v>Planned Playwright · tests/member5/ · M5_TC_014 (Offline - requires non-prod DB / staging rate limit)</v>
       </c>
       <c r="N15" t="str">
-        <v>Not Run</v>
-      </c>
-      <c r="O15" t="str">
-        <v>Unexecuted against live Vercel environment to adhere to project safety constraints (prohibiting production DB mutations / synthetic orders). Retained as validated specification.</v>
+        <v>-</v>
       </c>
     </row>
     <row r="16" xml:space="preserve">
       <c r="A16" t="str">
-        <v>Basis Path Testing (BP)</v>
+        <v>M5_TC_015</v>
       </c>
       <c r="B16" t="str">
         <v>Member 5</v>
       </c>
       <c r="C16" t="str">
-        <v>M5_TC_015</v>
+        <v>Order Status &amp; Cancellation</v>
       </c>
       <c r="D16" t="str">
-        <v>Order Status &amp; Cancellation</v>
+        <v>Basis Path</v>
       </c>
       <c r="E16" t="str">
-        <v>orderService.updateStatus</v>
+        <v>BP: updateStatus Path 2 - Cannot reopen already cancelled order</v>
       </c>
       <c r="F16" t="str">
-        <v>lib/services/order-service.ts</v>
-      </c>
-      <c r="G16" t="str">
-        <v>BP: updateStatus Path 2 - Cannot reopen already cancelled order</v>
-      </c>
-      <c r="H16" t="str">
-        <v>Admin attempts to change status from Cancelled to Processing</v>
-      </c>
-      <c r="I16" t="str">
-        <v>Current status="Cancelled", target status="Processing"</v>
-      </c>
-      <c r="J16" t="str">
         <v>Order is in Cancelled status</v>
       </c>
-      <c r="K16" t="str" xml:space="preserve">
+      <c r="G16" t="str" xml:space="preserve">
         <v xml:space="preserve">1. Call orderService.updateStatus(orderId, "Processing")
 2. Catch exception</v>
       </c>
+      <c r="H16" t="str">
+        <v>Current status="Cancelled", target status="Processing"</v>
+      </c>
+      <c r="I16" t="str">
+        <v>Throws ConflictError("Cannot reopen an already cancelled order")</v>
+      </c>
+      <c r="J16" t="str">
+        <v>ConflictError thrown, reopening prevented</v>
+      </c>
+      <c r="K16" t="str">
+        <v>Pass</v>
+      </c>
       <c r="L16" t="str">
-        <v>Throws ConflictError("Cannot reopen an already cancelled order")</v>
+        <v>Medium</v>
       </c>
       <c r="M16" t="str">
-        <v>ConflictError thrown, reopening prevented</v>
+        <v>Unit · tests/phase2a-regression.ts · Order State Transitions (M5_TC_015)</v>
       </c>
       <c r="N16" t="str">
-        <v>PASS</v>
-      </c>
-      <c r="O16" t="str">
-        <v>Verified via isolated automated test suite (project_final_testcase/member5/test_cases/ &amp; tests/phase2a-regression.ts); not executed against live production database.</v>
+        <v>-</v>
       </c>
     </row>
     <row r="17" xml:space="preserve">
       <c r="A17" t="str">
-        <v>Basis Path Testing (BP)</v>
+        <v>M5_TC_016</v>
       </c>
       <c r="B17" t="str">
         <v>Member 5</v>
       </c>
       <c r="C17" t="str">
-        <v>M5_TC_016</v>
+        <v>Order Status &amp; Cancellation</v>
       </c>
       <c r="D17" t="str">
-        <v>Order Status &amp; Cancellation</v>
+        <v>Basis Path</v>
       </c>
       <c r="E17" t="str">
-        <v>orderService.updateStatus</v>
+        <v>BP: updateStatus Path 3 - Transition to Cancelled restores product stock atomically</v>
       </c>
       <c r="F17" t="str">
-        <v>lib/services/order-service.ts</v>
-      </c>
-      <c r="G17" t="str">
-        <v>BP: updateStatus Path 3 - Transition to Cancelled restores product stock atomically</v>
-      </c>
-      <c r="H17" t="str">
-        <v>Customer or admin cancels active Pending order</v>
-      </c>
-      <c r="I17" t="str">
-        <v>Current status="Pending", target status="Cancelled", order has 2 items</v>
-      </c>
-      <c r="J17" t="str">
         <v>Order is currently Pending</v>
       </c>
-      <c r="K17" t="str" xml:space="preserve">
+      <c r="G17" t="str" xml:space="preserve">
         <v xml:space="preserve">1. Call orderService.updateStatus(orderId, "Cancelled")
 2. Check product stock in DB</v>
       </c>
+      <c r="H17" t="str">
+        <v>Current status="Pending", target status="Cancelled", order has 2 items</v>
+      </c>
+      <c r="I17" t="str">
+        <v>Status updated to Cancelled; cancelledAt set; product stock incremented by order item quantities</v>
+      </c>
+      <c r="J17" t="str">
+        <v>Status Cancelled and stock restored atomically</v>
+      </c>
+      <c r="K17" t="str">
+        <v>Pass</v>
+      </c>
       <c r="L17" t="str">
-        <v>Status updated to Cancelled; cancelledAt set; product stock incremented by order item quantities</v>
+        <v>Medium</v>
       </c>
       <c r="M17" t="str">
-        <v>Status Cancelled and stock restored atomically</v>
+        <v>Unit · tests/phase2a-regression.ts · Order State Transitions (M5_TC_016)</v>
       </c>
       <c r="N17" t="str">
-        <v>PASS</v>
-      </c>
-      <c r="O17" t="str">
-        <v>Verified via isolated automated test suite (project_final_testcase/member5/test_cases/ &amp; tests/phase2a-regression.ts); not executed against live production database.</v>
+        <v>-</v>
       </c>
     </row>
     <row r="18" xml:space="preserve">
       <c r="A18" t="str">
-        <v>Basis Path Testing (BP)</v>
+        <v>M5_TC_017</v>
       </c>
       <c r="B18" t="str">
         <v>Member 5</v>
       </c>
       <c r="C18" t="str">
-        <v>M5_TC_017</v>
+        <v>Order Status &amp; Cancellation</v>
       </c>
       <c r="D18" t="str">
-        <v>Order Status &amp; Cancellation</v>
+        <v>Basis Path</v>
       </c>
       <c r="E18" t="str">
-        <v>orderService.updateStatus</v>
+        <v>BP: updateStatus Path 4 - Concurrent cancellation race CAS guard prevents duplicate stock increment</v>
       </c>
       <c r="F18" t="str">
-        <v>lib/services/order-service.ts</v>
-      </c>
-      <c r="G18" t="str">
-        <v>BP: updateStatus Path 4 - Concurrent cancellation race CAS guard prevents duplicate stock increment</v>
-      </c>
-      <c r="H18" t="str">
-        <v>Two concurrent requests attempt to cancel the same order simultaneously</v>
-      </c>
-      <c r="I18" t="str">
-        <v>Concurrent cancellation race on orderId</v>
-      </c>
-      <c r="J18" t="str">
         <v>Order is currently Pending</v>
       </c>
-      <c r="K18" t="str" xml:space="preserve">
+      <c r="G18" t="str" xml:space="preserve">
         <v xml:space="preserve">1. Simulate two concurrent updateMany queries with status: { not: "Cancelled" }
 2. Verify stock restoration count</v>
       </c>
+      <c r="H18" t="str">
+        <v>Concurrent cancellation race on orderId</v>
+      </c>
+      <c r="I18" t="str">
+        <v>First request receives updateCheck.count === 1 and restores stock; second receives count === 0 and skips restoration</v>
+      </c>
+      <c r="J18" t="str">
+        <v>Stock restored exactly once, concurrent double-restoration prevented</v>
+      </c>
+      <c r="K18" t="str">
+        <v>Pass</v>
+      </c>
       <c r="L18" t="str">
-        <v>First request receives updateCheck.count === 1 and restores stock; second receives count === 0 and skips restoration</v>
+        <v>Medium</v>
       </c>
       <c r="M18" t="str">
-        <v>Stock restored exactly once, concurrent double-restoration prevented</v>
+        <v>Unit · tests/phase2a-regression.ts · Order State Transitions (M5_TC_017)</v>
       </c>
       <c r="N18" t="str">
-        <v>PASS</v>
-      </c>
-      <c r="O18" t="str">
-        <v>Verified via isolated automated test suite (project_final_testcase/member5/test_cases/ &amp; tests/phase2a-regression.ts); not executed against live production database.</v>
+        <v>-</v>
       </c>
     </row>
     <row r="19" xml:space="preserve">
       <c r="A19" t="str">
-        <v>Basis Path Testing (BP)</v>
+        <v>M5_TC_018</v>
       </c>
       <c r="B19" t="str">
         <v>Member 5</v>
       </c>
       <c r="C19" t="str">
-        <v>M5_TC_018</v>
+        <v>Order Privacy &amp; Inspection</v>
       </c>
       <c r="D19" t="str">
-        <v>Order Privacy &amp; Inspection</v>
+        <v>Basis Path</v>
       </c>
       <c r="E19" t="str">
-        <v>orderService.getOrder</v>
+        <v>BP: getOrder Path 1 - Customer accesses own order successfully</v>
       </c>
       <c r="F19" t="str">
-        <v>lib/services/order-service.ts</v>
-      </c>
-      <c r="G19" t="str">
-        <v>BP: getOrder Path 1 - Customer accesses own order successfully</v>
-      </c>
-      <c r="H19" t="str">
-        <v>Customer views order details of an order they placed</v>
-      </c>
-      <c r="I19" t="str">
-        <v>userId = "cust-1", orderId = "order-owned-by-cust-1", isAdmin = false</v>
-      </c>
-      <c r="J19" t="str">
         <v>Order was created by cust-1</v>
       </c>
-      <c r="K19" t="str" xml:space="preserve">
+      <c r="G19" t="str" xml:space="preserve">
         <v xml:space="preserve">1. Call orderService.getOrder("cust-1", "order-owned-by-cust-1", false)
 2. Inspect returned order</v>
       </c>
+      <c r="H19" t="str">
+        <v>userId = "cust-1", orderId = "order-owned-by-cust-1", isAdmin = false</v>
+      </c>
+      <c r="I19" t="str">
+        <v>Returns order with status, items, shipping details, and formatted pricing</v>
+      </c>
+      <c r="J19" t="str">
+        <v>As expected (In-memory simulation returns order for owning customer, throws 404 for unauthorized customer)</v>
+      </c>
+      <c r="K19" t="str">
+        <v>Pass</v>
+      </c>
       <c r="L19" t="str">
-        <v>Returns order with status, items, shipping details, and formatted pricing</v>
+        <v>Medium</v>
       </c>
       <c r="M19" t="str">
-        <v>Order returned successfully</v>
+        <v>Unit Simulation · tests/phase2a-regression.ts · Order Privacy &amp; Tenant Isolation (M5_TC_018)</v>
       </c>
       <c r="N19" t="str">
-        <v>PASS</v>
-      </c>
-      <c r="O19" t="str">
-        <v>Verified via isolated automated test suite (project_final_testcase/member5/test_cases/ &amp; tests/phase2a-regression.ts); not executed against live production database.</v>
+        <v>-</v>
       </c>
     </row>
     <row r="20" xml:space="preserve">
       <c r="A20" t="str">
-        <v>Equivalence Class Testing (ECT)</v>
+        <v>M5_TC_019</v>
       </c>
       <c r="B20" t="str">
         <v>Member 5</v>
       </c>
       <c r="C20" t="str">
-        <v>M5_TC_019</v>
+        <v>Order Privacy &amp; Inspection</v>
       </c>
       <c r="D20" t="str">
-        <v>Order Privacy &amp; Inspection</v>
+        <v>ECT</v>
       </c>
       <c r="E20" t="str">
-        <v>orderService.getOrder</v>
+        <v>ECT: Cross-tenant customer order isolation (unauthorized customer query)</v>
       </c>
       <c r="F20" t="str">
-        <v>lib/services/order-service.ts</v>
-      </c>
-      <c r="G20" t="str">
-        <v>ECT: Cross-tenant customer order isolation (unauthorized customer query)</v>
-      </c>
-      <c r="H20" t="str">
-        <v>Customer A attempts to inspect order placed by Customer B</v>
-      </c>
-      <c r="I20" t="str">
-        <v>session userId = "cust-A", target orderId = "order-placed-by-cust-B", isAdmin = false</v>
-      </c>
-      <c r="J20" t="str">
         <v>Order belongs to cust-B</v>
       </c>
-      <c r="K20" t="str" xml:space="preserve">
+      <c r="G20" t="str" xml:space="preserve">
         <v xml:space="preserve">1. Call orderService.getOrder("cust-A", "order-placed-by-cust-B", false)
 2. Catch exception</v>
       </c>
+      <c r="H20" t="str">
+        <v>session userId = "cust-A", target orderId = "order-placed-by-cust-B", isAdmin = false</v>
+      </c>
+      <c r="I20" t="str">
+        <v>Throws NotFoundError("Order", orderId) preventing customer data leakage</v>
+      </c>
+      <c r="J20" t="str">
+        <v>NotFoundError thrown; 404 returned protecting privacy</v>
+      </c>
+      <c r="K20" t="str">
+        <v>Pass</v>
+      </c>
       <c r="L20" t="str">
-        <v>Throws NotFoundError("Order", orderId) preventing customer data leakage</v>
+        <v>High</v>
       </c>
       <c r="M20" t="str">
-        <v>NotFoundError thrown; 404 returned protecting privacy</v>
+        <v>Unit · tests/phase2a-regression.ts · Order Privacy &amp; Price Integrity (M5_TC_019)</v>
       </c>
       <c r="N20" t="str">
-        <v>PASS</v>
-      </c>
-      <c r="O20" t="str">
-        <v>Verified via isolated automated test suite (project_final_testcase/member5/test_cases/ &amp; tests/phase2a-regression.ts); not executed against live production database.</v>
+        <v>-</v>
       </c>
     </row>
     <row r="21" xml:space="preserve">
       <c r="A21" t="str">
-        <v>Equivalence Class Testing (ECT)</v>
+        <v>M5_TC_020</v>
       </c>
       <c r="B21" t="str">
         <v>Member 5</v>
       </c>
       <c r="C21" t="str">
-        <v>M5_TC_020</v>
+        <v>Order Privacy &amp; Inspection</v>
       </c>
       <c r="D21" t="str">
-        <v>Order Privacy &amp; Inspection</v>
+        <v>ECT</v>
       </c>
       <c r="E21" t="str">
-        <v>orderService.getOrder</v>
+        <v>ECT: Admin order inspection bypasses tenant isolation</v>
       </c>
       <c r="F21" t="str">
-        <v>lib/services/order-service.ts</v>
-      </c>
-      <c r="G21" t="str">
-        <v>ECT: Admin order inspection bypasses tenant isolation</v>
-      </c>
-      <c r="H21" t="str">
-        <v>Administrator views customer order from Admin Orders portal</v>
-      </c>
-      <c r="I21" t="str">
-        <v>session userId = "admin-1", target orderId = "cust-order-1", isAdmin = true</v>
-      </c>
-      <c r="J21" t="str">
         <v>Session user has admin privileges</v>
       </c>
-      <c r="K21" t="str" xml:space="preserve">
+      <c r="G21" t="str" xml:space="preserve">
         <v xml:space="preserve">1. Call orderService.getOrder("admin-1", "cust-order-1", true)
 2. Inspect returned order</v>
       </c>
+      <c r="H21" t="str">
+        <v>session userId = "admin-1", target orderId = "cust-order-1", isAdmin = true</v>
+      </c>
+      <c r="I21" t="str">
+        <v>Returns complete order details bypasses userId constraint</v>
+      </c>
+      <c r="J21" t="str">
+        <v>Complete customer order returned to admin</v>
+      </c>
+      <c r="K21" t="str">
+        <v>Pass</v>
+      </c>
       <c r="L21" t="str">
-        <v>Returns complete order details bypasses userId constraint</v>
+        <v>Medium</v>
       </c>
       <c r="M21" t="str">
-        <v>Complete customer order returned to admin</v>
+        <v>Unit · tests/phase2a-regression.ts · Order Privacy &amp; Price Integrity (M5_TC_020)</v>
       </c>
       <c r="N21" t="str">
-        <v>PASS</v>
-      </c>
-      <c r="O21" t="str">
-        <v>Verified via isolated automated test suite (project_final_testcase/member5/test_cases/ &amp; tests/phase2a-regression.ts); not executed against live production database.</v>
+        <v>-</v>
       </c>
     </row>
     <row r="22" xml:space="preserve">
       <c r="A22" t="str">
-        <v>Equivalence Class Testing (ECT)</v>
+        <v>M5_TC_021</v>
       </c>
       <c r="B22" t="str">
         <v>Member 5</v>
       </c>
       <c r="C22" t="str">
-        <v>M5_TC_021</v>
+        <v>COD Checkout Flow</v>
       </c>
       <c r="D22" t="str">
-        <v>COD Checkout Flow</v>
+        <v>ECT</v>
       </c>
       <c r="E22" t="str">
-        <v>POST /api/orders/checkout</v>
+        <v>ECT: Payment-free Cash on Delivery checkout mode</v>
       </c>
       <c r="F22" t="str">
-        <v>app/api/orders/checkout/route.ts</v>
-      </c>
-      <c r="G22" t="str">
-        <v>ECT: Payment-free Cash on Delivery checkout mode</v>
-      </c>
-      <c r="H22" t="str">
-        <v>Customer completes checkout without supplying payment gateway card or token</v>
-      </c>
-      <c r="I22" t="str">
-        <v>Payload with shipping address and no payment token</v>
-      </c>
-      <c r="J22" t="str">
         <v>Payment gateway credentials omitted</v>
       </c>
-      <c r="K22" t="str" xml:space="preserve">
+      <c r="G22" t="str" xml:space="preserve">
         <v xml:space="preserve">1. Submit POST /api/orders/checkout
 2. Inspect created order status and payment provider</v>
       </c>
+      <c r="H22" t="str">
+        <v>Payload with shipping address and no payment token</v>
+      </c>
+      <c r="I22" t="str">
+        <v>Order status is "Pending"; payment provider is Stripe/COD default; requiresGatewayRedirect=false</v>
+      </c>
+      <c r="J22" t="str">
+        <v>Order initialized as Pending COD without gateway calls</v>
+      </c>
+      <c r="K22" t="str">
+        <v>Pass</v>
+      </c>
       <c r="L22" t="str">
-        <v>Order status is "Pending"; payment provider is Stripe/COD default; requiresGatewayRedirect=false</v>
+        <v>High</v>
       </c>
       <c r="M22" t="str">
-        <v>Order initialized as Pending COD without gateway calls</v>
+        <v>Unit · tests/phase2a-regression.ts · Order Privacy &amp; Price Integrity (M5_TC_021)</v>
       </c>
       <c r="N22" t="str">
-        <v>PASS</v>
-      </c>
-      <c r="O22" t="str">
-        <v>Verified via isolated automated test suite (project_final_testcase/member5/test_cases/ &amp; tests/phase2a-regression.ts); not executed against live production database.</v>
+        <v>-</v>
       </c>
     </row>
     <row r="23" xml:space="preserve">
       <c r="A23" t="str">
-        <v>Equivalence Class Testing (ECT)</v>
+        <v>M5_TC_022</v>
       </c>
       <c r="B23" t="str">
         <v>Member 5</v>
       </c>
       <c r="C23" t="str">
-        <v>M5_TC_022</v>
+        <v>Payment Gateway Safety</v>
       </c>
       <c r="D23" t="str">
-        <v>Payment Gateway Safety</v>
+        <v>ECT</v>
       </c>
       <c r="E23" t="str">
-        <v>POST /api/payments/create-intent</v>
+        <v>ECT: Unconfigured STRIPE_SECRET_KEY safely returns 503 Service Unavailable</v>
       </c>
       <c r="F23" t="str">
-        <v>app/api/payments/create-intent/route.ts</v>
-      </c>
-      <c r="G23" t="str">
-        <v>ECT: Unconfigured STRIPE_SECRET_KEY safely returns 503 Service Unavailable</v>
-      </c>
-      <c r="H23" t="str">
-        <v>Calling create-intent when payment gateway credentials are not configured</v>
-      </c>
-      <c r="I23" t="str">
-        <v>orderId = valid-order-uuid, STRIPE_SECRET_KEY = undefined</v>
-      </c>
-      <c r="J23" t="str">
         <v>STRIPE_SECRET_KEY omitted from environment</v>
       </c>
-      <c r="K23" t="str" xml:space="preserve">
+      <c r="G23" t="str" xml:space="preserve">
         <v xml:space="preserve">1. Submit POST /api/payments/create-intent with orderId
 2. Inspect response status</v>
       </c>
+      <c r="H23" t="str">
+        <v>orderId = valid-order-uuid, STRIPE_SECRET_KEY = undefined</v>
+      </c>
+      <c r="I23" t="str">
+        <v>HTTP 503 Service Unavailable: Online payment processing is currently disabled</v>
+      </c>
+      <c r="J23" t="str">
+        <v>HTTP 503 Service Unavailable returned cleanly</v>
+      </c>
+      <c r="K23" t="str">
+        <v>Pass</v>
+      </c>
       <c r="L23" t="str">
-        <v>HTTP 503 Service Unavailable: Online payment processing is currently disabled</v>
+        <v>Medium</v>
       </c>
       <c r="M23" t="str">
-        <v>HTTP 503 Service Unavailable returned cleanly</v>
+        <v>Unit · tests/phase2a-regression.ts · Order Privacy &amp; Price Integrity (M5_TC_022)</v>
       </c>
       <c r="N23" t="str">
-        <v>PASS</v>
-      </c>
-      <c r="O23" t="str">
-        <v>Verified via isolated automated test suite (project_final_testcase/member5/test_cases/ &amp; tests/phase2a-regression.ts); not executed against live production database.</v>
+        <v>-</v>
       </c>
     </row>
     <row r="24" xml:space="preserve">
       <c r="A24" t="str">
-        <v>Equivalence Class Testing (ECT)</v>
+        <v>M5_TC_023</v>
       </c>
       <c r="B24" t="str">
         <v>Member 5</v>
       </c>
       <c r="C24" t="str">
-        <v>M5_TC_023</v>
+        <v>Price Integrity</v>
       </c>
       <c r="D24" t="str">
-        <v>Price Integrity</v>
+        <v>ECT</v>
       </c>
       <c r="E24" t="str">
-        <v>orderService.checkout (subtotal calculation)</v>
+        <v>ECT: Server-side pricing integrity overrides client-tampered totals</v>
       </c>
       <c r="F24" t="str">
-        <v>lib/services/order-service.ts</v>
-      </c>
-      <c r="G24" t="str">
-        <v>ECT: Server-side pricing integrity overrides client-tampered totals</v>
-      </c>
-      <c r="H24" t="str">
-        <v>Malicious client modifies client-side price payload before submission</v>
-      </c>
-      <c r="I24" t="str">
-        <v>Client submits item price $0.01; database price is $59.99</v>
-      </c>
-      <c r="J24" t="str">
         <v>Product price in database is $59.99</v>
       </c>
-      <c r="K24" t="str" xml:space="preserve">
+      <c r="G24" t="str" xml:space="preserve">
         <v xml:space="preserve">1. Submit checkout request
 2. Inspect created OrderItem unitPrice and totalAmount</v>
       </c>
+      <c r="H24" t="str">
+        <v>Client submits item price $0.01; database price is $59.99</v>
+      </c>
+      <c r="I24" t="str">
+        <v>Server ignores client prices; computes subtotal from database product.price ($59.99 * quantity)</v>
+      </c>
+      <c r="J24" t="str">
+        <v>Server computed correct $59.99 total, overriding client attempt</v>
+      </c>
+      <c r="K24" t="str">
+        <v>Pass</v>
+      </c>
       <c r="L24" t="str">
-        <v>Server ignores client prices; computes subtotal from database product.price ($59.99 * quantity)</v>
+        <v>Medium</v>
       </c>
       <c r="M24" t="str">
-        <v>Server computed correct $59.99 total, overriding client attempt</v>
+        <v>Unit · tests/phase2a-regression.ts · Order Privacy &amp; Price Integrity (M5_TC_023)</v>
       </c>
       <c r="N24" t="str">
-        <v>PASS</v>
-      </c>
-      <c r="O24" t="str">
-        <v>Verified via isolated automated test suite (project_final_testcase/member5/test_cases/ &amp; tests/phase2a-regression.ts); not executed against live production database.</v>
+        <v>-</v>
       </c>
     </row>
     <row r="25" xml:space="preserve">
       <c r="A25" t="str">
-        <v>Equivalence Class Testing (ECT)</v>
+        <v>M5_TC_024</v>
       </c>
       <c r="B25" t="str">
         <v>Member 5</v>
       </c>
       <c r="C25" t="str">
-        <v>M5_TC_024</v>
+        <v>Admin Session Roles</v>
       </c>
       <c r="D25" t="str">
-        <v>Admin Session Roles</v>
+        <v>ECT</v>
       </c>
       <c r="E25" t="str">
-        <v>apiHandler / session.user.roles</v>
+        <v>ECT: Session typing detects admin privileges via roles array</v>
       </c>
       <c r="F25" t="str">
-        <v>app/api/orders/[id]/route.ts</v>
-      </c>
-      <c r="G25" t="str">
-        <v>ECT: Session typing detects admin privileges via roles array</v>
-      </c>
-      <c r="H25" t="str">
-        <v>User session contains roles array ["admin"] instead of legacy role string</v>
-      </c>
-      <c r="I25" t="str">
-        <v>session = { user: { id: "u1", roles: ["admin"] } }</v>
-      </c>
-      <c r="J25" t="str">
         <v>User authenticated via NextAuth</v>
       </c>
-      <c r="K25" t="str" xml:space="preserve">
+      <c r="G25" t="str" xml:space="preserve">
         <v xml:space="preserve">1. Evaluate isAdmin check in route: session.user.roles?.includes("admin")
 2. Check boolean result</v>
       </c>
+      <c r="H25" t="str">
+        <v>session = { user: { id: "u1", roles: ["admin"] } }</v>
+      </c>
+      <c r="I25" t="str">
+        <v>Evaluates to true, recognizing admin status from NextAuth roles array</v>
+      </c>
+      <c r="J25" t="str">
+        <v>Evaluated to true, admin authorized</v>
+      </c>
+      <c r="K25" t="str">
+        <v>Pass</v>
+      </c>
       <c r="L25" t="str">
-        <v>Evaluates to true, recognizing admin status from NextAuth roles array</v>
+        <v>Medium</v>
       </c>
       <c r="M25" t="str">
-        <v>Evaluated to true, admin authorized</v>
+        <v>Unit · tests/phase2a-regression.ts · Order Privacy &amp; Price Integrity (M5_TC_024)</v>
       </c>
       <c r="N25" t="str">
-        <v>PASS</v>
-      </c>
-      <c r="O25" t="str">
-        <v>Verified via isolated automated test suite (project_final_testcase/member5/test_cases/ &amp; tests/phase2a-regression.ts); not executed against live production database.</v>
+        <v>-</v>
       </c>
     </row>
     <row r="26" xml:space="preserve">
       <c r="A26" t="str">
-        <v>Decision Table Testing (DT)</v>
+        <v>M5_TC_025</v>
       </c>
       <c r="B26" t="str">
         <v>Member 5</v>
       </c>
       <c r="C26" t="str">
-        <v>M5_TC_025</v>
+        <v>Admin Revenue Analytics</v>
       </c>
       <c r="D26" t="str">
-        <v>Admin Revenue Analytics</v>
+        <v>Decision Table</v>
       </c>
       <c r="E26" t="str">
-        <v>GET /api/dashboard/metrics</v>
+        <v>DT: Revenue Aggregation - Order Status = Pending COD (Included in revenue)</v>
       </c>
       <c r="F26" t="str">
-        <v>app/api/dashboard/metrics/route.ts</v>
-      </c>
-      <c r="G26" t="str">
-        <v>DT: Revenue Aggregation - Order Status = Pending COD (Included in revenue)</v>
-      </c>
-      <c r="H26" t="str">
-        <v>Dashboard computes total revenue with active Pending COD orders present</v>
-      </c>
-      <c r="I26" t="str">
-        <v>Order 1: status="Pending", totalAmount=100.00</v>
-      </c>
-      <c r="J26" t="str">
         <v>Orders table contains Pending COD order</v>
       </c>
-      <c r="K26" t="str" xml:space="preserve">
+      <c r="G26" t="str" xml:space="preserve">
         <v xml:space="preserve">1. Execute revenue aggregate query with where: { status: { not: "Cancelled" } }
 2. Inspect sum</v>
       </c>
+      <c r="H26" t="str">
+        <v>Order 1: status="Pending", totalAmount=100.00</v>
+      </c>
+      <c r="I26" t="str">
+        <v>Pending COD order included in totalRevenue sum ($100.00)</v>
+      </c>
+      <c r="J26" t="str">
+        <v>Pending COD order included in revenue aggregation</v>
+      </c>
+      <c r="K26" t="str">
+        <v>Pass</v>
+      </c>
       <c r="L26" t="str">
-        <v>Pending COD order included in totalRevenue sum ($100.00)</v>
+        <v>Medium</v>
       </c>
       <c r="M26" t="str">
-        <v>Pending COD order included in revenue aggregation</v>
+        <v>Unit · tests/phase2a-regression.ts · Revenue Metrics &amp; Order Matrix (M5_TC_025)</v>
       </c>
       <c r="N26" t="str">
-        <v>PASS</v>
-      </c>
-      <c r="O26" t="str">
-        <v>Verified via isolated automated test suite (project_final_testcase/member5/test_cases/ &amp; tests/phase2a-regression.ts); not executed against live production database.</v>
+        <v>-</v>
       </c>
     </row>
     <row r="27" xml:space="preserve">
       <c r="A27" t="str">
-        <v>Decision Table Testing (DT)</v>
+        <v>M5_TC_026</v>
       </c>
       <c r="B27" t="str">
         <v>Member 5</v>
       </c>
       <c r="C27" t="str">
-        <v>M5_TC_026</v>
+        <v>Admin Revenue Analytics</v>
       </c>
       <c r="D27" t="str">
-        <v>Admin Revenue Analytics</v>
+        <v>Decision Table</v>
       </c>
       <c r="E27" t="str">
-        <v>GET /api/dashboard/metrics</v>
+        <v>DT: Revenue Aggregation - Order Status = Delivered (Included in revenue)</v>
       </c>
       <c r="F27" t="str">
-        <v>app/api/dashboard/metrics/route.ts</v>
-      </c>
-      <c r="G27" t="str">
-        <v>DT: Revenue Aggregation - Order Status = Delivered (Included in revenue)</v>
-      </c>
-      <c r="H27" t="str">
-        <v>Dashboard computes total revenue with completed Delivered orders present</v>
-      </c>
-      <c r="I27" t="str">
-        <v>Order 2: status="Delivered", totalAmount=250.00</v>
-      </c>
-      <c r="J27" t="str">
         <v>Orders table contains Delivered order</v>
       </c>
-      <c r="K27" t="str" xml:space="preserve">
+      <c r="G27" t="str" xml:space="preserve">
         <v xml:space="preserve">1. Execute revenue aggregate query
 2. Inspect sum</v>
       </c>
+      <c r="H27" t="str">
+        <v>Order 2: status="Delivered", totalAmount=250.00</v>
+      </c>
+      <c r="I27" t="str">
+        <v>Delivered order included in totalRevenue sum ($250.00)</v>
+      </c>
+      <c r="J27" t="str">
+        <v>Delivered order included in revenue aggregation</v>
+      </c>
+      <c r="K27" t="str">
+        <v>Pass</v>
+      </c>
       <c r="L27" t="str">
-        <v>Delivered order included in totalRevenue sum ($250.00)</v>
+        <v>Medium</v>
       </c>
       <c r="M27" t="str">
-        <v>Delivered order included in revenue aggregation</v>
+        <v>Unit · tests/phase2a-regression.ts · Revenue Metrics &amp; Order Matrix (M5_TC_026)</v>
       </c>
       <c r="N27" t="str">
-        <v>PASS</v>
-      </c>
-      <c r="O27" t="str">
-        <v>Verified via isolated automated test suite (project_final_testcase/member5/test_cases/ &amp; tests/phase2a-regression.ts); not executed against live production database.</v>
+        <v>-</v>
       </c>
     </row>
     <row r="28" xml:space="preserve">
       <c r="A28" t="str">
-        <v>Decision Table Testing (DT)</v>
+        <v>M5_TC_027</v>
       </c>
       <c r="B28" t="str">
         <v>Member 5</v>
       </c>
       <c r="C28" t="str">
-        <v>M5_TC_027</v>
+        <v>Admin Revenue Analytics</v>
       </c>
       <c r="D28" t="str">
-        <v>Admin Revenue Analytics</v>
+        <v>Decision Table</v>
       </c>
       <c r="E28" t="str">
-        <v>GET /api/dashboard/metrics</v>
+        <v>DT: Revenue Aggregation - Order Status = Cancelled (Excluded from revenue)</v>
       </c>
       <c r="F28" t="str">
-        <v>app/api/dashboard/metrics/route.ts</v>
-      </c>
-      <c r="G28" t="str">
-        <v>DT: Revenue Aggregation - Order Status = Cancelled (Excluded from revenue)</v>
-      </c>
-      <c r="H28" t="str">
-        <v>Dashboard computes total revenue with Cancelled orders present in database</v>
-      </c>
-      <c r="I28" t="str">
-        <v>Order 3: status="Cancelled", totalAmount=150.00</v>
-      </c>
-      <c r="J28" t="str">
         <v>Orders table contains Cancelled order of $150</v>
       </c>
-      <c r="K28" t="str" xml:space="preserve">
+      <c r="G28" t="str" xml:space="preserve">
         <v xml:space="preserve">1. Execute revenue aggregate query with where: { status: { not: "Cancelled" } }
 2. Verify total</v>
       </c>
+      <c r="H28" t="str">
+        <v>Order 3: status="Cancelled", totalAmount=150.00</v>
+      </c>
+      <c r="I28" t="str">
+        <v>Cancelled order strictly excluded; totalRevenue reflects only active pipeline orders</v>
+      </c>
+      <c r="J28" t="str">
+        <v>Cancelled order amount excluded from revenue</v>
+      </c>
+      <c r="K28" t="str">
+        <v>Pass</v>
+      </c>
       <c r="L28" t="str">
-        <v>Cancelled order strictly excluded; totalRevenue reflects only active pipeline orders</v>
+        <v>Medium</v>
       </c>
       <c r="M28" t="str">
-        <v>Cancelled order amount excluded from revenue</v>
+        <v>Unit · tests/phase2a-regression.ts · Revenue Metrics &amp; Order Matrix (M5_TC_027)</v>
       </c>
       <c r="N28" t="str">
-        <v>PASS</v>
-      </c>
-      <c r="O28" t="str">
-        <v>Verified via isolated automated test suite (project_final_testcase/member5/test_cases/ &amp; tests/phase2a-regression.ts); not executed against live production database.</v>
+        <v>-</v>
       </c>
     </row>
     <row r="29" xml:space="preserve">
       <c r="A29" t="str">
-        <v>Decision Table Testing (DT)</v>
+        <v>M5_TC_028</v>
       </c>
       <c r="B29" t="str">
         <v>Member 5</v>
       </c>
       <c r="C29" t="str">
-        <v>M5_TC_028</v>
+        <v>Order Lifecycle Matrix</v>
       </c>
       <c r="D29" t="str">
-        <v>Order Lifecycle Matrix</v>
+        <v>Decision Table</v>
       </c>
       <c r="E29" t="str">
-        <v>orderService.updateStatus</v>
+        <v>DT: State Transition Matrix - Current: Pending, Target: Cancelled (Allowed with stock restore)</v>
       </c>
       <c r="F29" t="str">
-        <v>lib/services/order-service.ts</v>
-      </c>
-      <c r="G29" t="str">
-        <v>DT: State Transition Matrix - Current: Pending, Target: Cancelled (Allowed with stock restore)</v>
-      </c>
-      <c r="H29" t="str">
-        <v>Admin cancels an unfulfilled order</v>
-      </c>
-      <c r="I29" t="str">
-        <v>Current status="Pending", target status="Cancelled"</v>
-      </c>
-      <c r="J29" t="str">
         <v>Order is in Pending state</v>
       </c>
-      <c r="K29" t="str" xml:space="preserve">
+      <c r="G29" t="str" xml:space="preserve">
         <v xml:space="preserve">1. Call orderService.updateStatus(orderId, "Cancelled")
 2. Inspect transition and stock</v>
       </c>
+      <c r="H29" t="str">
+        <v>Current status="Pending", target status="Cancelled"</v>
+      </c>
+      <c r="I29" t="str">
+        <v>Transition permitted; status set to Cancelled; stock restored</v>
+      </c>
+      <c r="J29" t="str">
+        <v>Transition permitted, stock restored</v>
+      </c>
+      <c r="K29" t="str">
+        <v>Pass</v>
+      </c>
       <c r="L29" t="str">
-        <v>Transition permitted; status set to Cancelled; stock restored</v>
+        <v>Medium</v>
       </c>
       <c r="M29" t="str">
-        <v>Transition permitted, stock restored</v>
+        <v>Unit · tests/phase2a-regression.ts · Revenue Metrics &amp; Order Matrix (M5_TC_028)</v>
       </c>
       <c r="N29" t="str">
-        <v>PASS</v>
-      </c>
-      <c r="O29" t="str">
-        <v>Verified via isolated automated test suite (project_final_testcase/member5/test_cases/ &amp; tests/phase2a-regression.ts); not executed against live production database.</v>
+        <v>-</v>
       </c>
     </row>
     <row r="30" xml:space="preserve">
       <c r="A30" t="str">
-        <v>Decision Table Testing (DT)</v>
+        <v>M5_TC_029</v>
       </c>
       <c r="B30" t="str">
         <v>Member 5</v>
       </c>
       <c r="C30" t="str">
-        <v>M5_TC_029</v>
+        <v>Order Lifecycle Matrix</v>
       </c>
       <c r="D30" t="str">
-        <v>Order Lifecycle Matrix</v>
+        <v>Decision Table</v>
       </c>
       <c r="E30" t="str">
-        <v>orderService.updateStatus</v>
+        <v>DT: State Transition Matrix - Current: Cancelled, Target: Shipped (Forbidden)</v>
       </c>
       <c r="F30" t="str">
-        <v>lib/services/order-service.ts</v>
-      </c>
-      <c r="G30" t="str">
-        <v>DT: State Transition Matrix - Current: Cancelled, Target: Shipped (Forbidden)</v>
-      </c>
-      <c r="H30" t="str">
-        <v>Attempting to ship an already cancelled order</v>
-      </c>
-      <c r="I30" t="str">
-        <v>Current status="Cancelled", target status="Shipped"</v>
-      </c>
-      <c r="J30" t="str">
         <v>Order is in Cancelled state</v>
       </c>
-      <c r="K30" t="str" xml:space="preserve">
+      <c r="G30" t="str" xml:space="preserve">
         <v xml:space="preserve">1. Call orderService.updateStatus(orderId, "Shipped")
 2. Catch exception</v>
       </c>
+      <c r="H30" t="str">
+        <v>Current status="Cancelled", target status="Shipped"</v>
+      </c>
+      <c r="I30" t="str">
+        <v>Transition forbidden; throws ConflictError 409</v>
+      </c>
+      <c r="J30" t="str">
+        <v>ConflictError thrown, invalid transition blocked</v>
+      </c>
+      <c r="K30" t="str">
+        <v>Pass</v>
+      </c>
       <c r="L30" t="str">
-        <v>Transition forbidden; throws ConflictError 409</v>
+        <v>Medium</v>
       </c>
       <c r="M30" t="str">
-        <v>ConflictError thrown, invalid transition blocked</v>
+        <v>Unit · tests/phase2a-regression.ts · Revenue Metrics &amp; Order Matrix (M5_TC_029)</v>
       </c>
       <c r="N30" t="str">
-        <v>PASS</v>
-      </c>
-      <c r="O30" t="str">
-        <v>Verified via isolated automated test suite (project_final_testcase/member5/test_cases/ &amp; tests/phase2a-regression.ts); not executed against live production database.</v>
+        <v>-</v>
       </c>
     </row>
     <row r="31" xml:space="preserve">
       <c r="A31" t="str">
-        <v>Decision Table Testing (DT)</v>
+        <v>M5_TC_030</v>
       </c>
       <c r="B31" t="str">
         <v>Member 5</v>
       </c>
       <c r="C31" t="str">
-        <v>M5_TC_030</v>
+        <v>Order Lifecycle Matrix</v>
       </c>
       <c r="D31" t="str">
-        <v>Order Lifecycle Matrix</v>
+        <v>Decision Table</v>
       </c>
       <c r="E31" t="str">
-        <v>orderService.updateStatus</v>
+        <v>DT: State Transition Matrix - Current: Processing, Target: Shipped (Allowed without stock change)</v>
       </c>
       <c r="F31" t="str">
-        <v>lib/services/order-service.ts</v>
-      </c>
-      <c r="G31" t="str">
-        <v>DT: State Transition Matrix - Current: Processing, Target: Shipped (Allowed without stock change)</v>
-      </c>
-      <c r="H31" t="str">
-        <v>Admin transitions packed order to shipped courier handover</v>
-      </c>
-      <c r="I31" t="str">
-        <v>Current status="Processing", target status="Shipped"</v>
-      </c>
-      <c r="J31" t="str">
         <v>Order is in Processing state</v>
       </c>
-      <c r="K31" t="str" xml:space="preserve">
+      <c r="G31" t="str" xml:space="preserve">
         <v xml:space="preserve">1. Call orderService.updateStatus(orderId, "Shipped")
 2. Inspect transition</v>
       </c>
+      <c r="H31" t="str">
+        <v>Current status="Processing", target status="Shipped"</v>
+      </c>
+      <c r="I31" t="str">
+        <v>Transition permitted; status set to Shipped; shippedAt recorded; stock unaltered</v>
+      </c>
+      <c r="J31" t="str">
+        <v>Not Run</v>
+      </c>
+      <c r="K31" t="str">
+        <v>Not Run</v>
+      </c>
       <c r="L31" t="str">
-        <v>Transition permitted; status set to Shipped; shippedAt recorded; stock unaltered</v>
+        <v>Medium</v>
       </c>
       <c r="M31" t="str">
-        <v>Not Run</v>
+        <v>Planned Playwright · tests/member5/ · M5_TC_030 (Offline - requires non-prod DB / staging rate limit)</v>
       </c>
       <c r="N31" t="str">
-        <v>Not Run</v>
-      </c>
-      <c r="O31" t="str">
-        <v>Unexecuted against live Vercel environment to adhere to project safety constraints (prohibiting production DB mutations / synthetic orders). Retained as validated specification.</v>
+        <v>-</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:O31"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:N31"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E18"/>
+  <cols>
+    <col min="1" max="1" width="18.83203125" customWidth="1"/>
+    <col min="2" max="2" width="25.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+    <col min="4" max="4" width="12.83203125" customWidth="1"/>
+    <col min="5" max="5" width="55.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Member 5 — Checkout Idempotency: Idempotency key length</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>Field: idempotencyKey   |   Rule: Optional string up to 100 characters (Zod string().max(100).optional())</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>Test case</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Input value</v>
+      </c>
+      <c r="C4" t="str">
+        <v>Boundary position</v>
+      </c>
+      <c r="D4" t="str">
+        <v>Class</v>
+      </c>
+      <c r="E4" t="str">
+        <v>Expected outcome</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>[Coverage]</v>
+      </c>
+      <c r="B5" t="str">
+        <v>1 char</v>
+      </c>
+      <c r="C5" t="str">
+        <v>min</v>
+      </c>
+      <c r="D5" t="str">
+        <v>Valid</v>
+      </c>
+      <c r="E5" t="str">
+        <v>Checkout executes successfully with 1-char key</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>[Coverage]</v>
+      </c>
+      <c r="B6" t="str">
+        <v>36 chars (UUID v4)</v>
+      </c>
+      <c r="C6" t="str">
+        <v>nominal typical</v>
+      </c>
+      <c r="D6" t="str">
+        <v>Valid</v>
+      </c>
+      <c r="E6" t="str">
+        <v>Checkout executes successfully with UUID key</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>[Coverage]</v>
+      </c>
+      <c r="B7" t="str">
+        <v>99 chars</v>
+      </c>
+      <c r="C7" t="str">
+        <v>max-1</v>
+      </c>
+      <c r="D7" t="str">
+        <v>Valid</v>
+      </c>
+      <c r="E7" t="str">
+        <v>Checkout executes successfully with 99-char key</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>M5_TC_005</v>
+      </c>
+      <c r="B8" t="str">
+        <v>100 chars</v>
+      </c>
+      <c r="C8" t="str">
+        <v>max</v>
+      </c>
+      <c r="D8" t="str">
+        <v>Valid</v>
+      </c>
+      <c r="E8" t="str">
+        <v>Checkout executes successfully with 100-char key</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>M5_TC_006</v>
+      </c>
+      <c r="B9" t="str">
+        <v>101 chars</v>
+      </c>
+      <c r="C9" t="str">
+        <v>max+1</v>
+      </c>
+      <c r="D9" t="str">
+        <v>Invalid</v>
+      </c>
+      <c r="E9" t="str">
+        <v>HTTP 400 Validation error: String exceeds 100 characters</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>Member 5 — Checkout Shipping: Address line 1 and notes</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>Field: line1 &amp; notes   |   Rule: line1 min(1), notes max(500) (Zod order schema)</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>Test case</v>
+      </c>
+      <c r="B14" t="str">
+        <v>Input value</v>
+      </c>
+      <c r="C14" t="str">
+        <v>Boundary position</v>
+      </c>
+      <c r="D14" t="str">
+        <v>Class</v>
+      </c>
+      <c r="E14" t="str">
+        <v>Expected outcome</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>M5_TC_001</v>
+      </c>
+      <c r="B15" t="str">
+        <v>0 (empty line1)</v>
+      </c>
+      <c r="C15" t="str">
+        <v>min-1</v>
+      </c>
+      <c r="D15" t="str">
+        <v>Invalid</v>
+      </c>
+      <c r="E15" t="str">
+        <v>HTTP 400 Validation error: Address is required</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>M5_TC_002</v>
+      </c>
+      <c r="B16" t="str">
+        <v>1 char line1</v>
+      </c>
+      <c r="C16" t="str">
+        <v>min</v>
+      </c>
+      <c r="D16" t="str">
+        <v>Valid</v>
+      </c>
+      <c r="E16" t="str">
+        <v>Checkout accepts 1-character street address</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>M5_TC_003</v>
+      </c>
+      <c r="B17" t="str">
+        <v>500 chars notes</v>
+      </c>
+      <c r="C17" t="str">
+        <v>max</v>
+      </c>
+      <c r="D17" t="str">
+        <v>Valid</v>
+      </c>
+      <c r="E17" t="str">
+        <v>Checkout accepts 500-character delivery notes</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>M5_TC_004</v>
+      </c>
+      <c r="B18" t="str">
+        <v>501 chars notes</v>
+      </c>
+      <c r="C18" t="str">
+        <v>max+1</v>
+      </c>
+      <c r="D18" t="str">
+        <v>Invalid</v>
+      </c>
+      <c r="E18" t="str">
+        <v>HTTP 400 Validation error: Notes exceed 500 characters</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:E18"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:G42"/>
+  <cols>
+    <col min="1" max="1" width="22.83203125" customWidth="1"/>
+    <col min="2" max="2" width="18.83203125" customWidth="1"/>
+    <col min="3" max="3" width="35.83203125" customWidth="1"/>
+    <col min="4" max="4" width="25.83203125" customWidth="1"/>
+    <col min="5" max="5" width="30.83203125" customWidth="1"/>
+    <col min="6" max="6" width="25.83203125" customWidth="1"/>
+    <col min="7" max="7" width="20.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Equivalence classes</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>Input</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Class</v>
+      </c>
+      <c r="C2" t="str">
+        <v>Description</v>
+      </c>
+      <c r="D2" t="str">
+        <v>Example</v>
+      </c>
+      <c r="E2" t="str">
+        <v>Test case(s)</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>Product Query Limit</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Valid</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Integer between 1 and 100</v>
+      </c>
+      <c r="D3" t="str">
+        <v>1, 20, 100</v>
+      </c>
+      <c r="E3" t="str">
+        <v>M1_TC_002, M1_TC_003, M1_TC_004</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>Product Query Limit</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Invalid</v>
+      </c>
+      <c r="C4" t="str">
+        <v>Less than 1 or greater than 100</v>
+      </c>
+      <c r="D4" t="str">
+        <v>0, 101, -5</v>
+      </c>
+      <c r="E4" t="str">
+        <v>M1_TC_001, M1_TC_005</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>Category Name</v>
+      </c>
+      <c r="B5" t="str">
+        <v>Valid</v>
+      </c>
+      <c r="C5" t="str">
+        <v>Non-empty string</v>
+      </c>
+      <c r="D5" t="str">
+        <v>"Laptops"</v>
+      </c>
+      <c r="E5" t="str">
+        <v>M1_TC_020</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>Category Name</v>
+      </c>
+      <c r="B6" t="str">
+        <v>Invalid</v>
+      </c>
+      <c r="C6" t="str">
+        <v>Blank or empty string</v>
+      </c>
+      <c r="D6" t="str">
+        <v>""</v>
+      </c>
+      <c r="E6" t="str">
+        <v>M1_TC_021</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>Category Parent ID</v>
+      </c>
+      <c r="B7" t="str">
+        <v>Valid</v>
+      </c>
+      <c r="C7" t="str">
+        <v>Valid existing UUID string</v>
+      </c>
+      <c r="D7" t="str">
+        <v>"e2b7c6c0-..."</v>
+      </c>
+      <c r="E7" t="str">
+        <v>M1_TC_022</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>Category Parent ID</v>
+      </c>
+      <c r="B8" t="str">
+        <v>Invalid</v>
+      </c>
+      <c r="C8" t="str">
+        <v>Malformed non-UUID string</v>
+      </c>
+      <c r="D8" t="str">
+        <v>"invalid-parent-uuid"</v>
+      </c>
+      <c r="E8" t="str">
+        <v>M1_TC_023</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>Cart Item Quantity</v>
+      </c>
+      <c r="B9" t="str">
+        <v>Valid</v>
+      </c>
+      <c r="C9" t="str">
+        <v>Integer between 1 and 99</v>
+      </c>
+      <c r="D9" t="str">
+        <v>1, 5, 99</v>
+      </c>
+      <c r="E9" t="str">
+        <v>M2_TC_002, M2_TC_018</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>Cart Item Quantity</v>
+      </c>
+      <c r="B10" t="str">
+        <v>Invalid</v>
+      </c>
+      <c r="C10" t="str">
+        <v>Negative number</v>
+      </c>
+      <c r="D10" t="str">
+        <v>-1</v>
+      </c>
+      <c r="E10" t="str">
+        <v>M2_TC_019</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>Cart Item Quantity</v>
+      </c>
+      <c r="B11" t="str">
+        <v>Invalid</v>
+      </c>
+      <c r="C11" t="str">
+        <v>String/non-numeric payload</v>
+      </c>
+      <c r="D11" t="str">
+        <v>"five"</v>
+      </c>
+      <c r="E11" t="str">
+        <v>M2_TC_020</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>Cart Product ID</v>
+      </c>
+      <c r="B12" t="str">
+        <v>Valid</v>
+      </c>
+      <c r="C12" t="str">
+        <v>Valid active product UUID</v>
+      </c>
+      <c r="D12" t="str">
+        <v>"a1b2c3d4-..."</v>
+      </c>
+      <c r="E12" t="str">
+        <v>M2_TC_021</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>Cart Product ID</v>
+      </c>
+      <c r="B13" t="str">
+        <v>Invalid</v>
+      </c>
+      <c r="C13" t="str">
+        <v>Non-UUID arbitrary string</v>
+      </c>
+      <c r="D13" t="str">
+        <v>"not-a-uuid"</v>
+      </c>
+      <c r="E13" t="str">
+        <v>M2_TC_022</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>Order Status Filter</v>
+      </c>
+      <c r="B14" t="str">
+        <v>Valid</v>
+      </c>
+      <c r="C14" t="str">
+        <v>Supported status (Pending, Delivered, etc.)</v>
+      </c>
+      <c r="D14" t="str">
+        <v>"Pending"</v>
+      </c>
+      <c r="E14" t="str">
+        <v>M3_TC_009</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>Order Status Filter</v>
+      </c>
+      <c r="B15" t="str">
+        <v>Invalid</v>
+      </c>
+      <c r="C15" t="str">
+        <v>Arbitrary unsupported string</v>
+      </c>
+      <c r="D15" t="str">
+        <v>"ShippedTomorrow"</v>
+      </c>
+      <c r="E15" t="str">
+        <v>M3_TC_010</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>Shipping Address</v>
+      </c>
+      <c r="B16" t="str">
+        <v>Valid</v>
+      </c>
+      <c r="C16" t="str">
+        <v>Complete shipping address fields</v>
+      </c>
+      <c r="D16" t="str">
+        <v>line1, city, country</v>
+      </c>
+      <c r="E16" t="str">
+        <v>M3_TC_011</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>Shipping Address</v>
+      </c>
+      <c r="B17" t="str">
+        <v>Invalid</v>
+      </c>
+      <c r="C17" t="str">
+        <v>Address payload missing city</v>
+      </c>
+      <c r="D17" t="str">
+        <v>line1 without city</v>
+      </c>
+      <c r="E17" t="str">
+        <v>M3_TC_012</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>Review Product ID</v>
+      </c>
+      <c r="B18" t="str">
+        <v>Valid</v>
+      </c>
+      <c r="C18" t="str">
+        <v>Valid product UUID</v>
+      </c>
+      <c r="D18" t="str">
+        <v>"c1d2e3f4-..."</v>
+      </c>
+      <c r="E18" t="str">
+        <v>M3_TC_013</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>Review Product ID</v>
+      </c>
+      <c r="B19" t="str">
+        <v>Invalid</v>
+      </c>
+      <c r="C19" t="str">
+        <v>Numeric or invalid string</v>
+      </c>
+      <c r="D19" t="str">
+        <v>"12345"</v>
+      </c>
+      <c r="E19" t="str">
+        <v>M3_TC_014</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>Registration Email</v>
+      </c>
+      <c r="B20" t="str">
+        <v>Valid</v>
+      </c>
+      <c r="C20" t="str">
+        <v>Unique RFC-compliant email address</v>
+      </c>
+      <c r="D20" t="str">
+        <v>"user@shopfinity.com"</v>
+      </c>
+      <c r="E20" t="str">
+        <v>M4_TC_009</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>Registration Email</v>
+      </c>
+      <c r="B21" t="str">
+        <v>Invalid</v>
+      </c>
+      <c r="C21" t="str">
+        <v>Missing @ symbol or domain delimiter</v>
+      </c>
+      <c r="D21" t="str">
+        <v>"usershopfinity.com"</v>
+      </c>
+      <c r="E21" t="str">
+        <v>M4_TC_010</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>Registration Email</v>
+      </c>
+      <c r="B22" t="str">
+        <v>Invalid</v>
+      </c>
+      <c r="C22" t="str">
+        <v>Empty email string</v>
+      </c>
+      <c r="D22" t="str">
+        <v>""</v>
+      </c>
+      <c r="E22" t="str">
+        <v>M4_TC_011</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>Registration Password</v>
+      </c>
+      <c r="B23" t="str">
+        <v>Valid</v>
+      </c>
+      <c r="C23" t="str">
+        <v>&gt;=8 chars with upper, lower, number, symbol</v>
+      </c>
+      <c r="D23" t="str">
+        <v>"Password123!"</v>
+      </c>
+      <c r="E23" t="str">
+        <v>M4_TC_009</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>Registration Password</v>
+      </c>
+      <c r="B24" t="str">
+        <v>Invalid</v>
+      </c>
+      <c r="C24" t="str">
+        <v>Missing uppercase letter</v>
+      </c>
+      <c r="D24" t="str">
+        <v>"password123!"</v>
+      </c>
+      <c r="E24" t="str">
+        <v>M4_TC_012</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>Registration Password</v>
+      </c>
+      <c r="B25" t="str">
+        <v>Invalid</v>
+      </c>
+      <c r="C25" t="str">
+        <v>Missing lowercase letter</v>
+      </c>
+      <c r="D25" t="str">
+        <v>"PASSWORD123!"</v>
+      </c>
+      <c r="E25" t="str">
+        <v>M4_TC_013</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>Registration Password</v>
+      </c>
+      <c r="B26" t="str">
+        <v>Invalid</v>
+      </c>
+      <c r="C26" t="str">
+        <v>Missing numeric digit</v>
+      </c>
+      <c r="D26" t="str">
+        <v>"Password!!!!"</v>
+      </c>
+      <c r="E26" t="str">
+        <v>M4_TC_014</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>Registration Password</v>
+      </c>
+      <c r="B27" t="str">
+        <v>Invalid</v>
+      </c>
+      <c r="C27" t="str">
+        <v>Missing special symbol</v>
+      </c>
+      <c r="D27" t="str">
+        <v>"Password1234"</v>
+      </c>
+      <c r="E27" t="str">
+        <v>M4_TC_015</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>Registration Password</v>
+      </c>
+      <c r="B28" t="str">
+        <v>Invalid</v>
+      </c>
+      <c r="C28" t="str">
+        <v>Fewer than 8 characters</v>
+      </c>
+      <c r="D28" t="str">
+        <v>"Pass1!"</v>
+      </c>
+      <c r="E28" t="str">
+        <v>M4_TC_016</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>Order Privacy Scope</v>
+      </c>
+      <c r="B29" t="str">
+        <v>Valid</v>
+      </c>
+      <c r="C29" t="str">
+        <v>Customer queries own placed order</v>
+      </c>
+      <c r="D29" t="str">
+        <v>Current user owns order</v>
+      </c>
+      <c r="E29" t="str">
+        <v>M5_TC_019</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>Order Privacy Scope</v>
+      </c>
+      <c r="B30" t="str">
+        <v>Invalid</v>
+      </c>
+      <c r="C30" t="str">
+        <v>Customer queries another tenant's order</v>
+      </c>
+      <c r="D30" t="str">
+        <v>Tenant boundary violation</v>
+      </c>
+      <c r="E30" t="str">
+        <v>M5_TC_019</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>Admin Order Scope</v>
+      </c>
+      <c r="B31" t="str">
+        <v>Valid</v>
+      </c>
+      <c r="C31" t="str">
+        <v>Admin session queries any customer order</v>
+      </c>
+      <c r="D31" t="str">
+        <v>isAdmin = true</v>
+      </c>
+      <c r="E31" t="str">
+        <v>M5_TC_020</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>COD Payment Payload</v>
+      </c>
+      <c r="B32" t="str">
+        <v>Valid</v>
+      </c>
+      <c r="C32" t="str">
+        <v>Null/omitted gateway credentials for COD</v>
+      </c>
+      <c r="D32" t="str">
+        <v>gateway token omitted</v>
+      </c>
+      <c r="E32" t="str">
+        <v>M5_TC_021</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>Stripe Secret Key</v>
+      </c>
+      <c r="B33" t="str">
+        <v>Invalid</v>
+      </c>
+      <c r="C33" t="str">
+        <v>Unconfigured STRIPE_SECRET_KEY env variable</v>
+      </c>
+      <c r="D33" t="str">
+        <v>undefined / null</v>
+      </c>
+      <c r="E33" t="str">
+        <v>M5_TC_022</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>Price Tampering</v>
+      </c>
+      <c r="B34" t="str">
+        <v>Invalid</v>
+      </c>
+      <c r="C34" t="str">
+        <v>Client submits modified subtotal price</v>
+      </c>
+      <c r="D34" t="str">
+        <v>client payload $1.00</v>
+      </c>
+      <c r="E34" t="str">
+        <v>M5_TC_023</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>Admin Roles Array</v>
+      </c>
+      <c r="B35" t="str">
+        <v>Valid</v>
+      </c>
+      <c r="C35" t="str">
+        <v>Session contains roles array ["admin"]</v>
+      </c>
+      <c r="D35" t="str">
+        <v>roles: ["admin"]</v>
+      </c>
+      <c r="E35" t="str">
+        <v>M5_TC_024</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>Decision table 4 — Order lifecycle &amp; status transitions (Member 5)</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>Rule</v>
+      </c>
+      <c r="B38" t="str">
+        <v>Current Status</v>
+      </c>
+      <c r="C38" t="str">
+        <v>Target Status</v>
+      </c>
+      <c r="D38" t="str">
+        <v>Is Admin?</v>
+      </c>
+      <c r="E38" t="str">
+        <v>Stock Action</v>
+      </c>
+      <c r="F38" t="str">
+        <v>Result</v>
+      </c>
+      <c r="G38" t="str">
+        <v>Test case</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>R1</v>
+      </c>
+      <c r="B39" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="C39" t="str">
+        <v>Cancelled</v>
+      </c>
+      <c r="D39" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="E39" t="str">
+        <v>Restock inventory items</v>
+      </c>
+      <c r="F39" t="str">
+        <v>200 Order Cancelled &amp; restocked</v>
+      </c>
+      <c r="G39" t="str">
+        <v>M5_TC_028</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>R2</v>
+      </c>
+      <c r="B40" t="str">
+        <v>Cancelled</v>
+      </c>
+      <c r="C40" t="str">
+        <v>Shipped</v>
+      </c>
+      <c r="D40" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="E40" t="str">
+        <v>None</v>
+      </c>
+      <c r="F40" t="str">
+        <v>400 Cannot transition out of Cancelled</v>
+      </c>
+      <c r="G40" t="str">
+        <v>M5_TC_029</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>R3</v>
+      </c>
+      <c r="B41" t="str">
+        <v>Processing</v>
+      </c>
+      <c r="C41" t="str">
+        <v>Shipped</v>
+      </c>
+      <c r="D41" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="E41" t="str">
+        <v>None</v>
+      </c>
+      <c r="F41" t="str">
+        <v>200 Order Shipped to courier</v>
+      </c>
+      <c r="G41" t="str">
+        <v>M5_TC_030</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>R4</v>
+      </c>
+      <c r="B42" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="C42" t="str">
+        <v>Delivered</v>
+      </c>
+      <c r="D42" t="str">
+        <v>No (Customer)</v>
+      </c>
+      <c r="E42" t="str">
+        <v>None</v>
+      </c>
+      <c r="F42" t="str">
+        <v>403 Forbidden: Admin required</v>
+      </c>
+      <c r="G42" t="str">
+        <v>M5_TC_020</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:G42"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:H14"/>
+  <cols>
+    <col min="1" max="1" width="18.83203125" customWidth="1"/>
+    <col min="2" max="2" width="28.83203125" customWidth="1"/>
+    <col min="3" max="3" width="32.83203125" customWidth="1"/>
+    <col min="4" max="4" width="18.83203125" customWidth="1"/>
+    <col min="5" max="5" width="45.83203125" customWidth="1"/>
+    <col min="6" max="6" width="22.83203125" customWidth="1"/>
+    <col min="7" max="7" width="30.83203125" customWidth="1"/>
+    <col min="8" max="8" width="38.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Basis Path Testing — Procedural Modules and Control Flow Metrics</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>Member</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Routine / Function</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Source File</v>
+      </c>
+      <c r="D3" t="str">
+        <v>Cyclomatic Complexity V(G)</v>
+      </c>
+      <c r="E3" t="str">
+        <v>Independent Basis Paths</v>
+      </c>
+      <c r="F3" t="str">
+        <v>Test Case IDs</v>
+      </c>
+      <c r="G3" t="str">
+        <v>Execution Evidence Type</v>
+      </c>
+      <c r="H3" t="str">
+        <v>Cross-Member Overlap Disclosure</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>Member 5</v>
+      </c>
+      <c r="B4" t="str">
+        <v>orderService.checkout</v>
+      </c>
+      <c r="C4" t="str">
+        <v>lib/services/order.service.ts</v>
+      </c>
+      <c r="D4">
+        <v>5</v>
+      </c>
+      <c r="E4" t="str">
+        <v>Path 1: Empty cart; Path 2: Stock validation halt; Path 3: Price tamper override; Path 4: COD pending order; Path 5: Cart cleared</v>
+      </c>
+      <c r="F4" t="str">
+        <v>M5_TC_007–M5_TC_010</v>
+      </c>
+      <c r="G4" t="str">
+        <v>Unit Pure Logic + Playwright API</v>
+      </c>
+      <c r="H4" t="str">
+        <v>Shared Routine (Also tested by Member 3)</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>Member 5</v>
+      </c>
+      <c r="B5" t="str">
+        <v>orderService.getAdminOrders</v>
+      </c>
+      <c r="C5" t="str">
+        <v>lib/services/order.service.ts</v>
+      </c>
+      <c r="D5">
+        <v>4</v>
+      </c>
+      <c r="E5" t="str">
+        <v>Path 1: Non-admin unauthorized (403); Path 2: Status filtered query; Path 3: Date range query; Path 4: Full order list with items</v>
+      </c>
+      <c r="F5" t="str">
+        <v>M5_TC_011</v>
+      </c>
+      <c r="G5" t="str">
+        <v>Playwright API Integration</v>
+      </c>
+      <c r="H5" t="str">
+        <v>Standalone (Member 5)</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>Member 5</v>
+      </c>
+      <c r="B6" t="str">
+        <v>orderService.updateStatus</v>
+      </c>
+      <c r="C6" t="str">
+        <v>lib/services/order.service.ts</v>
+      </c>
+      <c r="D6">
+        <v>5</v>
+      </c>
+      <c r="E6" t="str">
+        <v>Path 1: Order not found; Path 2: Invalid status transition; Path 3: Cancelled restocks; Path 4: Processing to Shipped; Path 5: Delivered</v>
+      </c>
+      <c r="F6" t="str">
+        <v>M5_TC_014–M5_TC_018</v>
+      </c>
+      <c r="G6" t="str">
+        <v>Unit State Machine + Playwright API</v>
+      </c>
+      <c r="H6" t="str">
+        <v>Shared Routine (Also tested by Member 3)</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>Member 5</v>
+      </c>
+      <c r="B7" t="str">
+        <v>handleApiError</v>
+      </c>
+      <c r="C7" t="str">
+        <v>lib/errors/index.ts</v>
+      </c>
+      <c r="D7">
+        <v>6</v>
+      </c>
+      <c r="E7" t="str">
+        <v>Path 1: SyntaxError with "JSON" (400); Path 2: SyntaxError with "end of JSON" (400); Path 3: AppError (preserves status); Path 4: ZodError (400); Path 5: Generic Error (500); Path 6: Non-Error primitive (500)</v>
+      </c>
+      <c r="F7" t="str">
+        <v>M5_TC_012</v>
+      </c>
+      <c r="G7" t="str">
+        <v>Direct Production Function Unit Test</v>
+      </c>
+      <c r="H7" t="str">
+        <v>Standalone (Member 5) (V(G)=6, 100% path coverage in phase2a-regression.ts)</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>Member 5</v>
+      </c>
+      <c r="B8" t="str">
+        <v>rateLimit</v>
+      </c>
+      <c r="C8" t="str">
+        <v>lib/rate-limit.ts</v>
+      </c>
+      <c r="D8">
+        <v>4</v>
+      </c>
+      <c r="E8" t="str">
+        <v>Path 1: New key initialization (allowed=true); Path 2: Within quota decrement (allowed=true); Path 3: Quota exceeded (allowed=false, resetIn&gt;0); Path 4: Expired window reset</v>
+      </c>
+      <c r="F8" t="str">
+        <v>M5_TC_013</v>
+      </c>
+      <c r="G8" t="str">
+        <v>Direct Production Function Unit Test</v>
+      </c>
+      <c r="H8" t="str">
+        <v>Standalone (Member 5) (V(G)=4, 100% path coverage in phase2a-regression.ts)</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>Rubric &amp; Allocation Notes:</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>1. Per-Member Allocation: Each of the 5 group members has exactly 5 clearly identified primary procedural routines (30 cases per member, 6 cases per routine domain).</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>2. Member 2 Routine Count: Member 2 has 5 primary backend/service routines plus 1 supplementary client UI routine (Navbar.itemCount badge, M2_TC_016–017).</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>3. Cross-Member Shared Routines: Across the entire team, 22 globally unique functions are tested because 3 routines span shared functional modules: (a) categoryService.delete (M1 &amp; M4), (b) orderService.checkout (M3 &amp; M5), (c) orderService.updateStatus (M3 &amp; M5).</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>4. Mock-Only Separation: categoryService.update and cartService.mergeCart are tested using in-memory mock logic in tests/phase2a-regression.ts to protect live Supabase production database from unsafe mutations. handleApiError and rateLimit are tested as direct production functions.</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:H14"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1"/>
+  <cols>
+    <col min="1" max="1" width="10.83203125" customWidth="1"/>
+    <col min="2" max="2" width="25.83203125" customWidth="1"/>
+    <col min="3" max="3" width="45.83203125" customWidth="1"/>
+    <col min="4" max="4" width="45.83203125" customWidth="1"/>
+    <col min="5" max="5" width="35.83203125" customWidth="1"/>
+    <col min="6" max="6" width="35.83203125" customWidth="1"/>
+    <col min="7" max="7" width="10.83203125" customWidth="1"/>
+    <col min="8" max="8" width="10.83203125" customWidth="1"/>
+    <col min="9" max="9" width="12.83203125" customWidth="1"/>
+    <col min="10" max="10" width="12.83203125" customWidth="1"/>
+    <col min="11" max="11" width="18.83203125" customWidth="1"/>
+    <col min="12" max="12" width="12.83203125" customWidth="1"/>
+  </cols>
+  <sheetData/>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D18"/>
+  <cols>
+    <col min="1" max="1" width="45.83203125" customWidth="1"/>
+    <col min="2" max="2" width="55.83203125" customWidth="1"/>
+    <col min="3" max="3" width="12.83203125" customWidth="1"/>
+    <col min="4" max="4" width="60.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Unit testing — tsx / Node runner (Pure Logic, Schemas &amp; Isolated In-Memory Mocks)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>File (tests/phase2a-regression.ts)</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Covers</v>
+      </c>
+      <c r="C2" t="str">
+        <v>Member</v>
+      </c>
+      <c r="D2" t="str">
+        <v>Run command</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>tests/phase2a-regression.ts</v>
+      </c>
+      <c r="B3" t="str">
+        <v>handleApiError (M5_TC_012): JSON SyntaxError, AppError, ValidationError, generic Error (6 paths)</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Member 5</v>
+      </c>
+      <c r="D3" t="str">
+        <v>npx tsx tests/phase2a-regression.ts</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>tests/phase2a-regression.ts</v>
+      </c>
+      <c r="B4" t="str">
+        <v>apiHandler pipeline (M5_TC_012): wraps JSON SyntaxError into HTTP 400 NextResponse</v>
+      </c>
+      <c r="C4" t="str">
+        <v>Member 5</v>
+      </c>
+      <c r="D4" t="str">
+        <v>npx tsx tests/phase2a-regression.ts</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>tests/phase2a-regression.ts</v>
+      </c>
+      <c r="B5" t="str">
+        <v>rateLimit (M5_TC_013): quota enforcement, threshold rejection, and expired window reset (4 paths)</v>
+      </c>
+      <c r="C5" t="str">
+        <v>Member 5</v>
+      </c>
+      <c r="D5" t="str">
+        <v>npx tsx tests/phase2a-regression.ts</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>tests/phase2a-regression.ts</v>
+      </c>
+      <c r="B6" t="str">
+        <v>rateLimitResponse pipeline (M5_TC_013): maps resetIn to HTTP 429 NextResponse with Retry-After header</v>
+      </c>
+      <c r="C6" t="str">
+        <v>Member 5</v>
+      </c>
+      <c r="D6" t="str">
+        <v>npx tsx tests/phase2a-regression.ts</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>tests/phase2a-regression.ts</v>
+      </c>
+      <c r="B7" t="str">
+        <v>Idempotency safety: cross-user collision rejection with ConflictError (409)</v>
+      </c>
+      <c r="C7" t="str">
+        <v>Member 5</v>
+      </c>
+      <c r="D7" t="str">
+        <v>npx tsx tests/phase2a-regression.ts</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>tests/phase2a-regression.ts</v>
+      </c>
+      <c r="B8" t="str">
+        <v>Payment gateway safety: unconfigured STRIPE_SECRET_KEY produces 503 Service Unavailable</v>
+      </c>
+      <c r="C8" t="str">
+        <v>Member 5</v>
+      </c>
+      <c r="D8" t="str">
+        <v>npx tsx tests/phase2a-regression.ts</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>tests/phase2a-regression.ts</v>
+      </c>
+      <c r="B9" t="str">
+        <v>Price integrity: server computes subtotal from DB product price, strictly overriding client payload</v>
+      </c>
+      <c r="C9" t="str">
+        <v>Member 5</v>
+      </c>
+      <c r="D9" t="str">
+        <v>npx tsx tests/phase2a-regression.ts</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>tests/phase2a-regression.ts</v>
+      </c>
+      <c r="B10" t="str">
+        <v>DEF-08 Admin revenue metrics exclude Cancelled orders from aggregation</v>
+      </c>
+      <c r="C10" t="str">
+        <v>Member 5</v>
+      </c>
+      <c r="D10" t="str">
+        <v>npx tsx tests/phase2a-regression.ts</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>Automation testing — Playwright (Browser UI + API Integration)</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>File (path)</v>
+      </c>
+      <c r="B13" t="str">
+        <v>Test cases</v>
+      </c>
+      <c r="C13" t="str">
+        <v>Member</v>
+      </c>
+      <c r="D13" t="str">
+        <v>Run command</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>tests/member5/test_cases/m5-bva.spec.ts</v>
+      </c>
+      <c r="B14" t="str">
+        <v>M5_TC_001 – M5_TC_006 (6)</v>
+      </c>
+      <c r="C14" t="str">
+        <v>Member 5</v>
+      </c>
+      <c r="D14" t="str">
+        <v>npx playwright test tests/member5/test_cases/m5-bva.spec.ts</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>tests/member5/test_cases/m5-bp.spec.ts</v>
+      </c>
+      <c r="B15" t="str">
+        <v>M5_TC_007 – M5_TC_018 (12)</v>
+      </c>
+      <c r="C15" t="str">
+        <v>Member 5</v>
+      </c>
+      <c r="D15" t="str">
+        <v>npx playwright test tests/member5/test_cases/m5-bp.spec.ts</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>tests/member5/test_cases/m5-ect.spec.ts</v>
+      </c>
+      <c r="B16" t="str">
+        <v>M5_TC_019 – M5_TC_024 (6)</v>
+      </c>
+      <c r="C16" t="str">
+        <v>Member 5</v>
+      </c>
+      <c r="D16" t="str">
+        <v>npx playwright test tests/member5/test_cases/m5-ect.spec.ts</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>tests/member5/test_cases/m5-dt.spec.ts</v>
+      </c>
+      <c r="B17" t="str">
+        <v>M5_TC_025 – M5_TC_030 (6)</v>
+      </c>
+      <c r="C17" t="str">
+        <v>Member 5</v>
+      </c>
+      <c r="D17" t="str">
+        <v>npx playwright test tests/member5/test_cases/m5-dt.spec.ts</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>tests/helpers/</v>
+      </c>
+      <c r="B18" t="str">
+        <v>Shared setup (API seeding, auth fixtures)</v>
+      </c>
+      <c r="C18" t="str">
+        <v>Team</v>
+      </c>
+      <c r="D18" t="str">
+        <v>-</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:D18"/>
   </ignoredErrors>
 </worksheet>
 </file>